--- a/chanas/presta/media/prestataire_soins2.xlsx
+++ b/chanas/presta/media/prestataire_soins2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/antboy/Desktop/PWC/CODE/venv/chanas_2/chanas/presta/media/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BE199527-EED4-F54F-A139-56FE28AE7A38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C1C8763-7689-F241-B1EA-466E1CCDA123}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{DAEB2858-4AB9-DC42-BCCA-AA77F40B5715}"/>
   </bookViews>
@@ -1598,9 +1598,6 @@
     <t>MAROUA</t>
   </si>
   <si>
-    <t>Type</t>
-  </si>
-  <si>
     <r>
       <t> </t>
     </r>
@@ -1647,6 +1644,9 @@
   </si>
   <si>
     <t>FOUNDATION</t>
+  </si>
+  <si>
+    <t>TYPE</t>
   </si>
 </sst>
 </file>
@@ -1797,7 +1797,7 @@
     <tableColumn id="2" xr3:uid="{2622A07C-27E5-7342-A004-FC36A3C08F04}" name="PRESTATAIRES" dataDxfId="2"/>
     <tableColumn id="3" xr3:uid="{0513F6E7-602A-ED46-8CFE-B9790B9A6BD2}" name="LIEU" dataDxfId="1"/>
     <tableColumn id="4" xr3:uid="{7CD384D9-9904-2640-B4D9-D31547083864}" name="TELEPHONE"/>
-    <tableColumn id="5" xr3:uid="{DFD4B9DD-90BB-F949-8950-AACF1FD0E6AD}" name="Type"/>
+    <tableColumn id="5" xr3:uid="{DFD4B9DD-90BB-F949-8950-AACF1FD0E6AD}" name="TYPE"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2144,7 +2144,7 @@
         <v>5</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
@@ -4769,7 +4769,7 @@
         <v>39</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.2">
@@ -4786,7 +4786,7 @@
         <v>41</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.2">
@@ -4803,7 +4803,7 @@
         <v>23</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.2">
@@ -4820,7 +4820,7 @@
         <v>25</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.2">
@@ -4837,7 +4837,7 @@
         <v>27</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.2">
@@ -4854,7 +4854,7 @@
         <v>29</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.2">
@@ -4871,7 +4871,7 @@
         <v>31</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.2">
@@ -4888,7 +4888,7 @@
         <v>33</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.2">
@@ -4905,7 +4905,7 @@
         <v>35</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.2">
@@ -4922,7 +4922,7 @@
         <v>37</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.2">
@@ -4939,7 +4939,7 @@
         <v>232</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.2">
@@ -4956,7 +4956,7 @@
         <v>43</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.2">
@@ -4973,7 +4973,7 @@
         <v>45</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.2">
@@ -4990,7 +4990,7 @@
         <v>47</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.2">
@@ -5007,7 +5007,7 @@
         <v>49</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.2">
@@ -5024,7 +5024,7 @@
         <v>51</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.2">
@@ -5041,7 +5041,7 @@
         <v>53</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.2">
@@ -5058,7 +5058,7 @@
         <v>55</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.2">
@@ -5075,7 +5075,7 @@
         <v>57</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.2">
@@ -5092,7 +5092,7 @@
         <v>59</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.2">
@@ -5109,7 +5109,7 @@
         <v>61</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.2">
@@ -5126,7 +5126,7 @@
         <v>63</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.2">
@@ -5143,7 +5143,7 @@
         <v>65</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.2">
@@ -5160,7 +5160,7 @@
         <v>67</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.2">
@@ -5177,7 +5177,7 @@
         <v>69</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.2">
@@ -5194,7 +5194,7 @@
         <v>71</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.2">
@@ -5211,7 +5211,7 @@
         <v>73</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.2">
@@ -5228,7 +5228,7 @@
         <v>75</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.2">
@@ -5245,7 +5245,7 @@
         <v>77</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.2">
@@ -5262,7 +5262,7 @@
         <v>79</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.2">
@@ -5279,7 +5279,7 @@
         <v>81</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.2">
@@ -5296,7 +5296,7 @@
         <v>83</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.2">
@@ -5313,7 +5313,7 @@
         <v>85</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.2">
@@ -5330,7 +5330,7 @@
         <v>87</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.2">
@@ -5347,7 +5347,7 @@
         <v>89</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.2">
@@ -5364,7 +5364,7 @@
         <v>91</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.2">
@@ -5381,7 +5381,7 @@
         <v>93</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.2">
@@ -5398,7 +5398,7 @@
         <v>95</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.2">
@@ -5415,7 +5415,7 @@
         <v>97</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.2">
@@ -5432,7 +5432,7 @@
         <v>99</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.2">
@@ -5449,7 +5449,7 @@
         <v>101</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.2">
@@ -5466,7 +5466,7 @@
         <v>103</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.2">
@@ -5483,7 +5483,7 @@
         <v>105</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.2">
@@ -5500,7 +5500,7 @@
         <v>107</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.2">
@@ -5517,7 +5517,7 @@
         <v>109</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.2">
@@ -5534,7 +5534,7 @@
         <v>111</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.2">
@@ -5551,7 +5551,7 @@
         <v>113</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.2">
@@ -5568,7 +5568,7 @@
         <v>115</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.2">
@@ -5585,7 +5585,7 @@
         <v>117</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.2">
@@ -5602,7 +5602,7 @@
         <v>119</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.2">
@@ -5619,7 +5619,7 @@
         <v>121</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.2">
@@ -5636,7 +5636,7 @@
         <v>123</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.2">
@@ -5653,7 +5653,7 @@
         <v>125</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.2">
@@ -5670,7 +5670,7 @@
         <v>125</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.2">
@@ -5687,7 +5687,7 @@
         <v>128</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.2">
@@ -5704,7 +5704,7 @@
         <v>130</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.2">
@@ -5721,7 +5721,7 @@
         <v>132</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.2">
@@ -5738,7 +5738,7 @@
         <v>134</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.2">
@@ -5755,7 +5755,7 @@
         <v>136</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.2">
@@ -5766,7 +5766,7 @@
         <v>0</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.2">
@@ -5823,7 +5823,7 @@
         <v>233</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.2">
@@ -5840,7 +5840,7 @@
         <v>234</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.2">
@@ -5888,7 +5888,7 @@
         <v>461</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.2">
@@ -5975,7 +5975,7 @@
         <v>244</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.2">
@@ -6167,7 +6167,7 @@
         <v>251</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.2">
@@ -6328,7 +6328,7 @@
         <v>257</v>
       </c>
       <c r="E262" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.2">
@@ -6345,7 +6345,7 @@
         <v>258</v>
       </c>
       <c r="E263" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.2">
@@ -6413,7 +6413,7 @@
         <v>262</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.2">
@@ -6430,7 +6430,7 @@
         <v>263</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.2">
@@ -6617,7 +6617,7 @@
         <v>270</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>

--- a/chanas/presta/media/prestataire_soins2.xlsx
+++ b/chanas/presta/media/prestataire_soins2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/antboy/Desktop/PWC/CODE/venv/chanas_2/chanas/presta/media/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C1C8763-7689-F241-B1EA-466E1CCDA123}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F82F244A-637C-6D4D-95CD-0236A0AED75A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{DAEB2858-4AB9-DC42-BCCA-AA77F40B5715}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1062" uniqueCount="525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1063" uniqueCount="526">
   <si>
     <t>DOUALA </t>
   </si>
@@ -1647,6 +1647,9 @@
   </si>
   <si>
     <t>TYPE</t>
+  </si>
+  <si>
+    <t>Total</t>
   </si>
 </sst>
 </file>
@@ -1718,7 +1721,43 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -1787,17 +1826,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0F51D3D8-888E-1F4D-8383-2294D5BEA7E8}" name="presta_soins" displayName="presta_soins" ref="A1:E282" totalsRowShown="0" headerRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0F51D3D8-888E-1F4D-8383-2294D5BEA7E8}" name="presta_soins" displayName="presta_soins" ref="A1:E283" totalsRowCount="1" headerRowDxfId="2">
   <autoFilter ref="A1:E282" xr:uid="{0F51D3D8-888E-1F4D-8383-2294D5BEA7E8}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A227:E227">
-    <sortCondition ref="E1:E282"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E282">
+    <sortCondition ref="A1:A282"/>
   </sortState>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{349BB440-2E5D-2843-AA4B-FAD92399387E}" name="CODE"/>
-    <tableColumn id="2" xr3:uid="{2622A07C-27E5-7342-A004-FC36A3C08F04}" name="PRESTATAIRES" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{0513F6E7-602A-ED46-8CFE-B9790B9A6BD2}" name="LIEU" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{349BB440-2E5D-2843-AA4B-FAD92399387E}" name="CODE" totalsRowLabel="Total"/>
+    <tableColumn id="2" xr3:uid="{2622A07C-27E5-7342-A004-FC36A3C08F04}" name="PRESTATAIRES" dataDxfId="4" totalsRowDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{0513F6E7-602A-ED46-8CFE-B9790B9A6BD2}" name="LIEU" dataDxfId="3" totalsRowDxfId="0"/>
     <tableColumn id="4" xr3:uid="{7CD384D9-9904-2640-B4D9-D31547083864}" name="TELEPHONE"/>
-    <tableColumn id="5" xr3:uid="{DFD4B9DD-90BB-F949-8950-AACF1FD0E6AD}" name="TYPE"/>
+    <tableColumn id="5" xr3:uid="{DFD4B9DD-90BB-F949-8950-AACF1FD0E6AD}" name="TYPE" totalsRowFunction="count"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2120,7 +2159,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E61D2BEC-D9B7-554D-8FA8-A40B60534B70}">
-  <dimension ref="A1:E282"/>
+  <dimension ref="A1:E283"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -2149,2811 +2188,2927 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
-        <v>66609</v>
+        <v>60001</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>328</v>
+        <v>78</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>212</v>
+        <v>79</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
-        <v>61065</v>
+        <v>60009</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>329</v>
+        <v>122</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>212</v>
+        <v>123</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
-        <v>61073</v>
+        <v>60023</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>330</v>
+        <v>112</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>212</v>
+        <v>113</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
-        <v>61019</v>
+        <v>60023</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>331</v>
+        <v>306</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>212</v>
+        <v>305</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
-        <v>61017</v>
+        <v>60025</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>332</v>
+        <v>100</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>212</v>
+        <v>101</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
-        <v>61132</v>
+        <v>60027</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>334</v>
+        <v>8</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>171</v>
-      </c>
       <c r="E7" s="2" t="s">
-        <v>212</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
-        <v>61074</v>
+        <v>60028</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>0</v>
+        <v>484</v>
+      </c>
+      <c r="C8" t="s">
+        <v>240</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>212</v>
+        <v>251</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
-        <v>61135</v>
+        <v>60029</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>336</v>
+        <v>38</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>212</v>
+        <v>39</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>521</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
-        <v>61121</v>
+        <v>60030</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>174</v>
+        <v>378</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>170</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>212</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
-        <v>61046</v>
+        <v>60036</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>0</v>
+        <v>373</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>170</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>175</v>
+        <v>201</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>212</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
-        <v>61101</v>
+        <v>60037</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>0</v>
+        <v>372</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>170</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>176</v>
+        <v>200</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>212</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
-        <v>61092</v>
+        <v>60063</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>340</v>
+        <v>64</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>212</v>
+      <c r="D13" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
-        <v>66748</v>
+        <v>60084</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>341</v>
+        <v>58</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>212</v>
+        <v>59</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
-        <v>66560</v>
+        <v>60107</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>0</v>
+        <v>455</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>517</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>212</v>
+        <v>232</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>520</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
-        <v>66705</v>
+        <v>60116</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>0</v>
+        <v>375</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>170</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>179</v>
+        <v>376</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>212</v>
+        <v>137</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
-        <v>64041</v>
+        <v>60118</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>344</v>
+        <v>9</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>180</v>
+        <v>10</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>212</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
-        <v>66776</v>
+        <v>60127</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>0</v>
+        <v>477</v>
+      </c>
+      <c r="C18" t="s">
+        <v>240</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>181</v>
+        <v>245</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>212</v>
+        <v>137</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
-        <v>66794</v>
+        <v>60194</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>346</v>
+        <v>60</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>212</v>
+        <v>61</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
-        <v>66802</v>
+        <v>60198</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>0</v>
+        <v>384</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>170</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>183</v>
+        <v>385</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
-        <v>61025</v>
+        <v>60208</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>348</v>
+        <v>32</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>212</v>
+        <v>33</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>520</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
-        <v>61080</v>
+        <v>60246</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>170</v>
+        <v>323</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>0</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>426</v>
+        <v>161</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>212</v>
+        <v>321</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
-        <v>61043</v>
+        <v>60248</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>427</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>170</v>
+        <v>80</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>0</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>428</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>212</v>
+        <v>81</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
-        <v>61081</v>
+        <v>60258</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>429</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>170</v>
+        <v>298</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>0</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>430</v>
+        <v>142</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>212</v>
+        <v>296</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="3">
-        <v>61079</v>
+        <v>60299</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>431</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>170</v>
+        <v>24</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>0</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>212</v>
+        <v>25</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>520</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="3">
-        <v>61134</v>
+        <v>60303</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>432</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>212</v>
+        <v>108</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="3">
-        <v>62050</v>
+        <v>60308</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>433</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>170</v>
+        <v>322</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>0</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>214</v>
+        <v>161</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>212</v>
+        <v>321</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="3">
-        <v>66566</v>
+        <v>60313</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>434</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>170</v>
+        <v>26</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>0</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>212</v>
+        <v>27</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>520</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" s="3">
-        <v>62133</v>
+        <v>60315</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>435</v>
+        <v>497</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>170</v>
+        <v>505</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>216</v>
+        <v>261</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>212</v>
+        <v>137</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="3">
-        <v>66704</v>
+        <v>60335</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>436</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>217</v>
+        <v>16</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>0</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>212</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" s="3">
-        <v>62137</v>
+        <v>60340</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>170</v>
+        <v>364</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>0</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>218</v>
+        <v>197</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>212</v>
+        <v>349</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" s="3">
-        <v>66667</v>
+        <v>60356</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>437</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>170</v>
+        <v>76</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>0</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>212</v>
+        <v>77</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" s="3">
-        <v>66646</v>
+        <v>60361</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>438</v>
+        <v>498</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>212</v>
+        <v>505</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" s="3">
-        <v>66506</v>
+        <v>60365</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>439</v>
+        <v>499</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>170</v>
+        <v>505</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>212</v>
+        <v>263</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" s="3">
-        <v>62009</v>
+        <v>60385</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>440</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>170</v>
+        <v>300</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>144</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>212</v>
+        <v>296</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" s="3">
-        <v>66662</v>
+        <v>60394</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>441</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>170</v>
+        <v>70</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>0</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>212</v>
+        <v>71</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" s="3">
-        <v>66524</v>
+        <v>60401</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>170</v>
+        <v>66</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>0</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>212</v>
+        <v>67</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" s="3">
-        <v>62088</v>
+        <v>60402</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>443</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>170</v>
+        <v>62</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>0</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>212</v>
+        <v>63</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" s="3">
-        <v>62103</v>
+        <v>60403</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>444</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>170</v>
+        <v>46</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>0</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>212</v>
+        <v>47</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" s="3">
-        <v>66730</v>
+        <v>60406</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>445</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>170</v>
+        <v>299</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>143</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>212</v>
+        <v>296</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" s="3">
-        <v>62145</v>
+        <v>60407</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>212</v>
+        <v>102</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" s="3">
-        <v>66722</v>
+        <v>60409</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>446</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>170</v>
+        <v>68</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>0</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>212</v>
+        <v>69</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" s="3">
-        <v>62128</v>
+        <v>60410</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>447</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>170</v>
+        <v>98</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>0</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>212</v>
+        <v>99</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A44" s="3">
+        <v>60414</v>
+      </c>
       <c r="B44" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>170</v>
+        <v>48</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>0</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>212</v>
+        <v>49</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A45" s="3">
+        <v>60415</v>
+      </c>
       <c r="B45" s="3" t="s">
-        <v>449</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>170</v>
+        <v>104</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>0</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>212</v>
+        <v>105</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A46" s="3">
+        <v>60420</v>
+      </c>
       <c r="B46" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>170</v>
+        <v>56</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>0</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>212</v>
+        <v>57</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A47" s="3">
+        <v>60430</v>
+      </c>
       <c r="B47" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>451</v>
+        <v>241</v>
+      </c>
+      <c r="C47" t="s">
+        <v>519</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>212</v>
+        <v>137</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A48" s="3">
+        <v>60438</v>
+      </c>
       <c r="B48" s="3" t="s">
-        <v>452</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>170</v>
+        <v>301</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>230</v>
+        <v>145</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>212</v>
+        <v>296</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49" s="3">
-        <v>66745</v>
+        <v>60442</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>453</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>517</v>
+        <v>297</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>0</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>231</v>
+        <v>141</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>212</v>
+        <v>296</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50" s="3">
-        <v>62050</v>
+        <v>60447</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>350</v>
+        <v>74</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>349</v>
+        <v>75</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51" s="3">
-        <v>66506</v>
+        <v>60449</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>351</v>
+        <v>54</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>349</v>
+        <v>55</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52" s="3">
-        <v>62133</v>
+        <v>60450</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>352</v>
+        <v>118</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>349</v>
+        <v>119</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53" s="3">
-        <v>62149</v>
+        <v>60457</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>353</v>
+        <v>124</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>0</v>
       </c>
+      <c r="D53" s="3" t="s">
+        <v>166</v>
+      </c>
       <c r="E53" s="2" t="s">
-        <v>349</v>
+        <v>321</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54" s="3">
-        <v>62057</v>
+        <v>60457</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>354</v>
+        <v>327</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>349</v>
+        <v>321</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55" s="3">
-        <v>66700</v>
+        <v>60458</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>355</v>
+        <v>52</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>349</v>
+        <v>53</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56" s="3">
-        <v>62143</v>
+        <v>60459</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>356</v>
+        <v>11</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>0</v>
       </c>
+      <c r="D56" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="E56" s="2" t="s">
-        <v>349</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57" s="3">
-        <v>62150</v>
+        <v>60481</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>0</v>
+        <v>397</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>170</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>190</v>
+        <v>398</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>349</v>
+        <v>205</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58" s="3">
-        <v>62109</v>
+        <v>60501</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>0</v>
+        <v>493</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>492</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>349</v>
+        <v>257</v>
+      </c>
+      <c r="E58" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59" s="3">
-        <v>62110</v>
+        <v>60900</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>192</v>
+        <v>379</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>170</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>349</v>
+        <v>137</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60" s="3">
-        <v>62115</v>
+        <v>60952</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>0</v>
+        <v>380</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>170</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>193</v>
+        <v>381</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>349</v>
+        <v>138</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61" s="3">
-        <v>62140</v>
+        <v>60975</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>0</v>
+        <v>496</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>243</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>194</v>
+        <v>260</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>349</v>
+        <v>137</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62" s="3">
-        <v>66564</v>
+        <v>60978</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>0</v>
+        <v>421</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>170</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>349</v>
+        <v>422</v>
+      </c>
+      <c r="E62" s="4" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63" s="3">
-        <v>66564</v>
+        <v>60980</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>0</v>
+        <v>485</v>
+      </c>
+      <c r="C63" t="s">
+        <v>240</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>196</v>
+        <v>252</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>349</v>
+        <v>138</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64" s="3">
-        <v>60340</v>
+        <v>60983</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>197</v>
+        <v>488</v>
+      </c>
+      <c r="C64" t="s">
+        <v>519</v>
+      </c>
+      <c r="D64" s="3">
+        <v>699101960</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>349</v>
+        <v>137</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65" s="3">
-        <v>66578</v>
+        <v>60991</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>198</v>
+        <v>474</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="D65" s="3">
+        <v>695475025</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>349</v>
+        <v>137</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66" s="3">
-        <v>66624</v>
+        <v>60992</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>199</v>
+        <v>478</v>
+      </c>
+      <c r="C66" t="s">
+        <v>240</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>349</v>
+        <v>137</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A67" s="3">
+        <v>60998</v>
+      </c>
       <c r="B67" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>0</v>
+        <v>386</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>387</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>349</v>
+        <v>204</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A68" s="3">
+        <v>60999</v>
+      </c>
       <c r="B68" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>0</v>
+        <v>391</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>392</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>349</v>
+        <v>204</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A69" s="3">
+        <v>61017</v>
+      </c>
       <c r="B69" s="3" t="s">
-        <v>369</v>
+        <v>332</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>0</v>
       </c>
+      <c r="D69" s="3" t="s">
+        <v>333</v>
+      </c>
       <c r="E69" s="2" t="s">
-        <v>349</v>
+        <v>212</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A70" s="3">
+        <v>61019</v>
+      </c>
       <c r="B70" s="3" t="s">
-        <v>370</v>
+        <v>331</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>0</v>
       </c>
+      <c r="D70" s="3" t="s">
+        <v>177</v>
+      </c>
       <c r="E70" s="2" t="s">
-        <v>349</v>
+        <v>212</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A71" s="3">
+        <v>61025</v>
+      </c>
       <c r="B71" s="3" t="s">
-        <v>371</v>
+        <v>348</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>0</v>
       </c>
+      <c r="D71" s="3" t="s">
+        <v>184</v>
+      </c>
       <c r="E71" s="2" t="s">
-        <v>349</v>
+        <v>212</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72" s="3">
-        <v>60442</v>
+        <v>61043</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>0</v>
+        <v>427</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>170</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>141</v>
+        <v>428</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>296</v>
+        <v>212</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73" s="3">
-        <v>60258</v>
+        <v>61046</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>298</v>
+        <v>338</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>142</v>
+        <v>175</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>296</v>
+        <v>212</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74" s="3">
-        <v>60406</v>
+        <v>61065</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>299</v>
+        <v>329</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>143</v>
+        <v>168</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>296</v>
+        <v>212</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75" s="3">
-        <v>60385</v>
+        <v>61073</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>300</v>
+        <v>330</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>144</v>
+        <v>169</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>296</v>
+        <v>212</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76" s="3">
-        <v>60438</v>
+        <v>61074</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>301</v>
+        <v>335</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>145</v>
+        <v>172</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>296</v>
+        <v>212</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A77" s="3">
-        <v>66612</v>
+        <v>61079</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>0</v>
+        <v>431</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>170</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>146</v>
+        <v>213</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>296</v>
+        <v>212</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78" s="3">
-        <v>66502</v>
+        <v>61080</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>0</v>
+        <v>425</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>170</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>147</v>
+        <v>426</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>296</v>
+        <v>212</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A79" s="3"/>
+      <c r="A79" s="3">
+        <v>61081</v>
+      </c>
       <c r="B79" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>0</v>
+        <v>429</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>170</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>148</v>
+        <v>430</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>296</v>
+        <v>212</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A80" s="3">
-        <v>60481</v>
+        <v>61092</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="D80" s="3" t="s">
-        <v>398</v>
+        <v>340</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>0</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A81" s="3">
+        <v>61100</v>
+      </c>
       <c r="B81" s="3" t="s">
-        <v>399</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>170</v>
+        <v>483</v>
+      </c>
+      <c r="C81" t="s">
+        <v>240</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>250</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82" s="3">
-        <v>63028</v>
+        <v>61101</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>415</v>
+        <v>491</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>170</v>
+        <v>492</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="E82" s="4" t="s">
-        <v>209</v>
+        <v>256</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83" s="3">
-        <v>63019</v>
+        <v>61101</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>170</v>
+        <v>339</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>0</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="E83" s="4" t="s">
-        <v>209</v>
+        <v>176</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84" s="3">
-        <v>66613</v>
+        <v>61121</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>419</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>170</v>
+        <v>337</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>0</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="E84" s="4" t="s">
-        <v>209</v>
+        <v>174</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A85" s="3">
-        <v>60978</v>
+        <v>61122</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>421</v>
+        <v>500</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>170</v>
+        <v>505</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>422</v>
-      </c>
-      <c r="E85" s="4" t="s">
-        <v>209</v>
+        <v>264</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A86" s="3">
-        <v>66614</v>
+        <v>61132</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>423</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>170</v>
+        <v>334</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>0</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>424</v>
-      </c>
-      <c r="E86" s="4" t="s">
-        <v>209</v>
+        <v>171</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A87" s="3">
+        <v>61134</v>
+      </c>
       <c r="B87" s="3" t="s">
-        <v>210</v>
+        <v>432</v>
       </c>
       <c r="C87" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="E87" s="4" t="s">
-        <v>209</v>
+      <c r="E87" s="2" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A88" s="3">
+        <v>61135</v>
+      </c>
       <c r="B88" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="E88" s="4" t="s">
-        <v>209</v>
+        <v>336</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A89" s="3">
-        <v>60023</v>
+        <v>62009</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D89" s="3" t="s">
-        <v>149</v>
+        <v>440</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>170</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>305</v>
+        <v>212</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A90" s="3">
-        <v>63001</v>
+        <v>62039</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>0</v>
+        <v>359</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>461</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="E90" s="2" t="s">
-        <v>305</v>
+        <v>237</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A91" s="3">
-        <v>63029</v>
+        <v>62039</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>0</v>
+        <v>359</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>505</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>151</v>
+        <v>267</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>305</v>
+        <v>349</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A92" s="3">
-        <v>63004</v>
+        <v>62050</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>309</v>
+        <v>350</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>152</v>
+        <v>185</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>305</v>
+        <v>349</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A93" s="3">
-        <v>63048</v>
+        <v>62050</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>0</v>
+        <v>433</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>170</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>153</v>
+        <v>214</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>305</v>
+        <v>212</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A94" s="3">
-        <v>63030</v>
+        <v>62057</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>311</v>
+        <v>354</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>154</v>
+        <v>188</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>305</v>
+        <v>349</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A95" s="3">
-        <v>66585</v>
+        <v>62088</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>0</v>
+        <v>443</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>170</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>155</v>
+        <v>223</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>305</v>
+        <v>212</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A96" s="3">
-        <v>63049</v>
+        <v>62103</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>0</v>
+        <v>444</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>170</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>156</v>
+        <v>224</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>305</v>
+        <v>212</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A97" s="3">
-        <v>66531</v>
+        <v>62109</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>314</v>
+        <v>358</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>157</v>
+        <v>191</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>305</v>
+        <v>349</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A98" s="3">
-        <v>66509</v>
+        <v>62110</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>315</v>
+        <v>359</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>158</v>
+        <v>192</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>305</v>
+        <v>349</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A99" s="3">
-        <v>66793</v>
+        <v>62115</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>316</v>
+        <v>360</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>159</v>
+        <v>193</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>305</v>
+        <v>349</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A100" s="3">
-        <v>66800</v>
+        <v>62128</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>0</v>
+        <v>447</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>170</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>160</v>
+        <v>226</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>305</v>
+        <v>212</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A101" s="3">
-        <v>66574</v>
+        <v>62129</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>0</v>
+        <v>489</v>
+      </c>
+      <c r="C101" t="s">
+        <v>519</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>305</v>
+        <v>349</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A102" s="3">
+        <v>62133</v>
+      </c>
       <c r="B102" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>0</v>
+        <v>435</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>216</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>305</v>
+        <v>212</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A103" s="3">
+        <v>62133</v>
+      </c>
       <c r="B103" s="3" t="s">
-        <v>320</v>
+        <v>352</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>0</v>
       </c>
+      <c r="D103" s="3" t="s">
+        <v>187</v>
+      </c>
       <c r="E103" s="2" t="s">
-        <v>305</v>
+        <v>349</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A104" s="3">
-        <v>60308</v>
+        <v>62137</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>0</v>
+        <v>370</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>170</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>161</v>
+        <v>218</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>321</v>
+        <v>212</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A105" s="3">
-        <v>60246</v>
+        <v>62140</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>323</v>
+        <v>361</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>161</v>
+        <v>194</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>321</v>
+        <v>349</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A106" s="3">
-        <v>66735</v>
+        <v>62143</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>324</v>
+        <v>356</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D106" s="3" t="s">
-        <v>162</v>
-      </c>
       <c r="E106" s="2" t="s">
-        <v>321</v>
+        <v>349</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A107" s="3">
-        <v>66576</v>
+        <v>62145</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="C107" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D107" s="3" t="s">
-        <v>163</v>
+        <v>362</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>170</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>321</v>
+        <v>212</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A108" s="3">
-        <v>66576</v>
+        <v>62149</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>326</v>
+        <v>353</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D108" s="3" t="s">
-        <v>164</v>
-      </c>
       <c r="E108" s="2" t="s">
-        <v>321</v>
+        <v>349</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A109" s="3">
-        <v>60457</v>
+        <v>62150</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>327</v>
+        <v>357</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>321</v>
+        <v>349</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A110" s="3">
-        <v>60457</v>
+        <v>62153</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="C110" s="2" t="s">
-        <v>0</v>
+        <v>486</v>
+      </c>
+      <c r="C110" t="s">
+        <v>240</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>166</v>
+        <v>253</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>321</v>
+        <v>349</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A111" s="3">
-        <v>66777</v>
+        <v>62154</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C111" s="2" t="s">
-        <v>0</v>
+        <v>501</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>505</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>125</v>
+        <v>265</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>321</v>
+        <v>349</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A112" s="2">
-        <v>66641</v>
+      <c r="A112" s="3">
+        <v>63001</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>6</v>
+        <v>307</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>7</v>
+        <v>150</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>1</v>
+        <v>305</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A113" s="3">
-        <v>60027</v>
+        <v>63004</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>8</v>
+        <v>309</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>0</v>
       </c>
+      <c r="D113" s="3" t="s">
+        <v>152</v>
+      </c>
       <c r="E113" s="2" t="s">
-        <v>1</v>
+        <v>305</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A114" s="3">
-        <v>60118</v>
+        <v>63019</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C114" s="2" t="s">
-        <v>0</v>
+        <v>417</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>170</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E114" s="2" t="s">
-        <v>1</v>
+        <v>418</v>
+      </c>
+      <c r="E114" s="4" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A115" s="3">
-        <v>60459</v>
+        <v>63028</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C115" s="2" t="s">
-        <v>0</v>
+        <v>415</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>170</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E115" s="2" t="s">
-        <v>1</v>
+        <v>416</v>
+      </c>
+      <c r="E115" s="4" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A116" s="3">
-        <v>66632</v>
+        <v>63029</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>12</v>
+        <v>308</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>13</v>
+        <v>151</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>1</v>
+        <v>305</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A117" s="3">
-        <v>66708</v>
+        <v>63030</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>14</v>
+        <v>311</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>15</v>
+        <v>154</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>1</v>
+        <v>305</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A118" s="3">
-        <v>60335</v>
+        <v>63043</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C118" s="2" t="s">
-        <v>0</v>
+        <v>481</v>
+      </c>
+      <c r="C118" t="s">
+        <v>240</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>248</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>1</v>
+        <v>138</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A119" s="3">
-        <v>66772</v>
+        <v>63048</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>17</v>
+        <v>310</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>18</v>
+        <v>153</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>1</v>
+        <v>305</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A120" s="3">
-        <v>66785</v>
+        <v>63049</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>19</v>
+        <v>313</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>0</v>
       </c>
+      <c r="D120" s="3" t="s">
+        <v>156</v>
+      </c>
       <c r="E120" s="2" t="s">
-        <v>1</v>
+        <v>305</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A121" s="3">
-        <v>66774</v>
+        <v>63053</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C121" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="E121" s="2" t="s">
-        <v>1</v>
+        <v>503</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>505</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A122" s="3">
+        <v>64017</v>
+      </c>
       <c r="B122" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C122" s="2" t="s">
-        <v>0</v>
+        <v>411</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>412</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>1</v>
+        <v>206</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A123" s="3">
-        <v>66806</v>
+        <v>64033</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>454</v>
+        <v>207</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>517</v>
+        <v>170</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>1</v>
+        <v>206</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A124" s="3">
+        <v>64041</v>
+      </c>
       <c r="B124" s="3" t="s">
-        <v>456</v>
-      </c>
-      <c r="C124" s="3" t="s">
-        <v>517</v>
+        <v>344</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>180</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>1</v>
+        <v>212</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A125" s="3">
-        <v>60037</v>
+        <v>64043</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="C125" s="3" t="s">
-        <v>170</v>
+        <v>282</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>0</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>200</v>
+        <v>283</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A126" s="3">
-        <v>60036</v>
+        <v>64054</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="C126" s="3" t="s">
-        <v>170</v>
+        <v>273</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>0</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>201</v>
+        <v>274</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A127" s="3">
-        <v>66525</v>
+        <v>64055</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>374</v>
+        <v>410</v>
       </c>
       <c r="C127" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="D127" s="3" t="s">
-        <v>202</v>
-      </c>
       <c r="E127" s="2" t="s">
-        <v>137</v>
+        <v>206</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A128" s="3">
-        <v>60116</v>
+        <v>64063</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>375</v>
+        <v>408</v>
       </c>
       <c r="C128" s="3" t="s">
         <v>170</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>376</v>
+        <v>409</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>137</v>
+        <v>206</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A129" s="3">
-        <v>66520</v>
+        <v>64067</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="C129" s="3" t="s">
-        <v>170</v>
+        <v>277</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D129" s="3" t="s">
+        <v>278</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A130" s="3">
-        <v>60030</v>
+        <v>64068</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="C130" s="3" t="s">
-        <v>170</v>
+        <v>275</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D130" s="3" t="s">
+        <v>276</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A131" s="3">
-        <v>60900</v>
+        <v>64070</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>379</v>
+        <v>406</v>
       </c>
       <c r="C131" s="3" t="s">
         <v>170</v>
       </c>
+      <c r="D131" s="3" t="s">
+        <v>407</v>
+      </c>
       <c r="E131" s="2" t="s">
-        <v>137</v>
+        <v>206</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A132" s="3">
-        <v>60952</v>
+        <v>64072</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>380</v>
+        <v>405</v>
       </c>
       <c r="C132" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="D132" s="3" t="s">
-        <v>381</v>
-      </c>
       <c r="E132" s="2" t="s">
-        <v>138</v>
+        <v>206</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A133" s="3">
+        <v>64080</v>
+      </c>
       <c r="B133" s="3" t="s">
-        <v>382</v>
+        <v>208</v>
       </c>
       <c r="C133" s="3" t="s">
         <v>170</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>138</v>
+        <v>206</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A134" s="3">
-        <v>66805</v>
+        <v>64091</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>203</v>
+        <v>400</v>
       </c>
       <c r="C134" s="3" t="s">
         <v>170</v>
       </c>
+      <c r="D134" s="3" t="s">
+        <v>401</v>
+      </c>
       <c r="E134" s="2" t="s">
-        <v>138</v>
+        <v>206</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A135" s="3">
+        <v>64091</v>
+      </c>
       <c r="B135" s="3" t="s">
-        <v>383</v>
+        <v>402</v>
       </c>
       <c r="C135" s="3" t="s">
         <v>170</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>138</v>
+        <v>206</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A136" s="3">
-        <v>60198</v>
+        <v>64905</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="C136" s="3" t="s">
-        <v>170</v>
+        <v>284</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>0</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>385</v>
+        <v>285</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>204</v>
+        <v>139</v>
       </c>
     </row>
     <row r="137" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="3">
-        <v>60998</v>
+        <v>66004</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="C137" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="D137" s="3" t="s">
-        <v>387</v>
-      </c>
       <c r="E137" s="2" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A138" s="3">
-        <v>66602</v>
+        <v>66467</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="C138" s="3" t="s">
-        <v>170</v>
+        <v>94</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>0</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="E138" s="2" t="s">
-        <v>204</v>
+        <v>95</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A139" s="3">
-        <v>66004</v>
+        <v>66502</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="C139" s="3" t="s">
-        <v>170</v>
+        <v>303</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D139" s="3" t="s">
+        <v>147</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>204</v>
+        <v>296</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A140" s="3">
-        <v>60999</v>
+        <v>66504</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>391</v>
+        <v>460</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>170</v>
+        <v>461</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="E140" s="2" t="s">
-        <v>204</v>
+        <v>233</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A141" s="3">
-        <v>66751</v>
+        <v>66505</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="C141" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="E141" s="2" t="s">
-        <v>204</v>
+        <v>44</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D141" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A142" s="3">
+        <v>66506</v>
+      </c>
       <c r="B142" s="3" t="s">
-        <v>394</v>
+        <v>439</v>
       </c>
       <c r="C142" s="3" t="s">
         <v>170</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>395</v>
+        <v>220</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A143" s="3">
+        <v>66506</v>
+      </c>
       <c r="B143" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="C143" s="3" t="s">
-        <v>170</v>
+        <v>351</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D143" s="3" t="s">
+        <v>186</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>204</v>
+        <v>349</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A144" s="3">
-        <v>64054</v>
+        <v>66509</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>273</v>
+        <v>315</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>274</v>
+        <v>158</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>139</v>
+        <v>305</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A145" s="3">
-        <v>64068</v>
+        <v>66510</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="C145" s="2" t="s">
-        <v>0</v>
+        <v>403</v>
+      </c>
+      <c r="C145" s="3" t="s">
+        <v>170</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>276</v>
+        <v>404</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>139</v>
+        <v>206</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A146" s="3">
-        <v>64067</v>
+        <v>66513</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="C146" s="2" t="s">
-        <v>0</v>
+        <v>469</v>
+      </c>
+      <c r="C146" s="3" t="s">
+        <v>470</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>278</v>
+        <v>471</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A147" s="3">
-        <v>66731</v>
+        <v>66518</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="C147" s="2" t="s">
-        <v>0</v>
+        <v>482</v>
+      </c>
+      <c r="C147" t="s">
+        <v>240</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>280</v>
+        <v>249</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A148" s="3">
-        <v>66575</v>
+        <v>66520</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="C148" s="2" t="s">
-        <v>0</v>
+        <v>377</v>
+      </c>
+      <c r="C148" s="3" t="s">
+        <v>170</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A149" s="3">
-        <v>64043</v>
+        <v>66524</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="C149" s="2" t="s">
-        <v>0</v>
+        <v>442</v>
+      </c>
+      <c r="C149" s="3" t="s">
+        <v>170</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>283</v>
+        <v>222</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>139</v>
+        <v>212</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A150" s="3">
-        <v>64905</v>
+        <v>66525</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="C150" s="2" t="s">
-        <v>0</v>
+        <v>374</v>
+      </c>
+      <c r="C150" s="3" t="s">
+        <v>170</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>285</v>
+        <v>202</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A151" s="3">
-        <v>66715</v>
+        <v>66531</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>286</v>
+        <v>314</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>287</v>
+        <v>157</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>139</v>
+        <v>305</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A152" s="3">
-        <v>66749</v>
+        <v>66538</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>288</v>
+        <v>40</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="E152" s="2" t="s">
-        <v>139</v>
+        <v>41</v>
+      </c>
+      <c r="E152" s="1" t="s">
+        <v>521</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A153" s="3">
-        <v>66756</v>
+        <v>66544</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>290</v>
+        <v>50</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="E153" s="2" t="s">
-        <v>139</v>
+        <v>51</v>
+      </c>
+      <c r="E153" s="1" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A154" s="3">
-        <v>66775</v>
+        <v>66560</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>292</v>
+        <v>342</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>293</v>
+        <v>178</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>139</v>
+        <v>212</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A155" s="3">
+        <v>66564</v>
+      </c>
       <c r="B155" s="3" t="s">
-        <v>294</v>
+        <v>362</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>0</v>
       </c>
+      <c r="D155" s="3" t="s">
+        <v>195</v>
+      </c>
       <c r="E155" s="2" t="s">
-        <v>139</v>
+        <v>349</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A156" s="3">
+        <v>66564</v>
+      </c>
       <c r="B156" s="3" t="s">
-        <v>295</v>
+        <v>363</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>140</v>
+        <v>196</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>139</v>
+        <v>349</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A157" s="3">
-        <v>64091</v>
+        <v>66564</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>400</v>
+        <v>476</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="D157" s="3" t="s">
-        <v>401</v>
+        <v>518</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>206</v>
+        <v>349</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A158" s="3">
-        <v>64091</v>
+        <v>66566</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>402</v>
+        <v>434</v>
       </c>
       <c r="C158" s="3" t="s">
         <v>170</v>
       </c>
+      <c r="D158" s="3" t="s">
+        <v>215</v>
+      </c>
       <c r="E158" s="2" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A159" s="3">
-        <v>66510</v>
+        <v>66574</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="C159" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="D159" s="3" t="s">
-        <v>404</v>
+        <v>318</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>0</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>206</v>
+        <v>305</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A160" s="3">
-        <v>64072</v>
+        <v>66575</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="C160" s="3" t="s">
-        <v>170</v>
+        <v>281</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>0</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>206</v>
+        <v>139</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A161" s="3">
-        <v>64070</v>
+        <v>66576</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="C161" s="3" t="s">
-        <v>170</v>
+        <v>325</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>0</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>407</v>
+        <v>163</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>206</v>
+        <v>321</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A162" s="3">
-        <v>64063</v>
+        <v>66576</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="C162" s="3" t="s">
-        <v>170</v>
+        <v>326</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>0</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>409</v>
+        <v>164</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>206</v>
+        <v>321</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A163" s="3">
-        <v>64055</v>
+        <v>66578</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="C163" s="3" t="s">
-        <v>170</v>
+        <v>365</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D163" s="3" t="s">
+        <v>198</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>206</v>
+        <v>349</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A164" s="3">
-        <v>64033</v>
+        <v>66585</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="C164" s="3" t="s">
-        <v>170</v>
+        <v>312</v>
+      </c>
+      <c r="C164" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D164" s="3" t="s">
+        <v>155</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>206</v>
+        <v>305</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A165" s="3">
-        <v>64017</v>
+        <v>66600</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>411</v>
-      </c>
-      <c r="C165" s="3" t="s">
-        <v>170</v>
+        <v>22</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>0</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="E165" s="2" t="s">
-        <v>206</v>
+        <v>23</v>
+      </c>
+      <c r="E165" s="1" t="s">
+        <v>520</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A166" s="3">
-        <v>64080</v>
+        <v>66602</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>208</v>
+        <v>388</v>
       </c>
       <c r="C166" s="3" t="s">
         <v>170</v>
       </c>
+      <c r="D166" s="3" t="s">
+        <v>389</v>
+      </c>
       <c r="E166" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A167" s="3">
-        <v>60029</v>
+        <v>66609</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>38</v>
+        <v>328</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E167" s="1" t="s">
-        <v>521</v>
+        <v>167</v>
+      </c>
+      <c r="E167" s="2" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A168" s="3">
-        <v>66538</v>
+        <v>66612</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>40</v>
+        <v>302</v>
       </c>
       <c r="C168" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E168" s="1" t="s">
-        <v>521</v>
+        <v>146</v>
+      </c>
+      <c r="E168" s="2" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A169" s="3">
-        <v>66600</v>
+        <v>66613</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C169" s="2" t="s">
-        <v>0</v>
+        <v>419</v>
+      </c>
+      <c r="C169" s="3" t="s">
+        <v>170</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E169" s="1" t="s">
-        <v>520</v>
+        <v>420</v>
+      </c>
+      <c r="E169" s="4" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A170" s="3">
-        <v>60299</v>
+        <v>66614</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C170" s="2" t="s">
-        <v>0</v>
+        <v>423</v>
+      </c>
+      <c r="C170" s="3" t="s">
+        <v>170</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E170" s="1" t="s">
-        <v>520</v>
+        <v>424</v>
+      </c>
+      <c r="E170" s="4" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A171" s="3">
-        <v>60313</v>
+        <v>66620</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="C171" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>27</v>
+        <v>97</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A172" s="3">
-        <v>66694</v>
+        <v>66622</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="C172" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>29</v>
+        <v>91</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A173" s="3">
-        <v>66768</v>
+        <v>66624</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>30</v>
+        <v>366</v>
       </c>
       <c r="C173" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E173" s="1" t="s">
-        <v>520</v>
+        <v>199</v>
+      </c>
+      <c r="E173" s="2" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A174" s="3">
-        <v>60208</v>
+        <v>66629</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C174" s="2" t="s">
-        <v>0</v>
+        <v>502</v>
+      </c>
+      <c r="C174" s="3" t="s">
+        <v>505</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E174" s="1" t="s">
-        <v>520</v>
+        <v>266</v>
+      </c>
+      <c r="E174" s="2" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A175" s="3">
-        <v>66773</v>
+        <v>66631</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C175" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D175" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E175" s="1" t="s">
-        <v>520</v>
+        <v>242</v>
+      </c>
+      <c r="C175" t="s">
+        <v>519</v>
+      </c>
+      <c r="E175" s="2" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A176" s="3">
-        <v>66799</v>
+        <v>66632</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="C176" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E176" s="1" t="s">
-        <v>520</v>
+        <v>13</v>
+      </c>
+      <c r="E176" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A177" s="3">
-        <v>60107</v>
+      <c r="A177" s="2">
+        <v>66641</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="C177" s="3" t="s">
-        <v>517</v>
+        <v>6</v>
+      </c>
+      <c r="C177" s="2" t="s">
+        <v>0</v>
       </c>
       <c r="D177" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="E177" s="1" t="s">
-        <v>520</v>
+        <v>7</v>
+      </c>
+      <c r="E177" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A178" s="3">
-        <v>66757</v>
+        <v>66642</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="C178" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="E178" s="1" t="s">
         <v>522</v>
@@ -4961,33 +5116,30 @@
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A179" s="3">
-        <v>66505</v>
+        <v>66646</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C179" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D179" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E179" s="1" t="s">
-        <v>522</v>
+        <v>438</v>
+      </c>
+      <c r="C179" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="E179" s="2" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A180" s="3">
-        <v>60403</v>
+        <v>66660</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>46</v>
+        <v>82</v>
       </c>
       <c r="C180" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="E180" s="1" t="s">
         <v>522</v>
@@ -4995,67 +5147,64 @@
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A181" s="3">
-        <v>60414</v>
+        <v>66662</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C181" s="2" t="s">
-        <v>0</v>
+        <v>441</v>
+      </c>
+      <c r="C181" s="3" t="s">
+        <v>170</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E181" s="1" t="s">
-        <v>522</v>
+        <v>221</v>
+      </c>
+      <c r="E181" s="2" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A182" s="3">
-        <v>66544</v>
+        <v>66664</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C182" s="2" t="s">
-        <v>0</v>
+        <v>487</v>
+      </c>
+      <c r="C182" t="s">
+        <v>240</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E182" s="1" t="s">
-        <v>522</v>
+        <v>254</v>
+      </c>
+      <c r="E182" s="2" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A183" s="3">
-        <v>60458</v>
+        <v>66667</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C183" s="2" t="s">
-        <v>0</v>
+        <v>437</v>
+      </c>
+      <c r="C183" s="3" t="s">
+        <v>170</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E183" s="1" t="s">
-        <v>522</v>
+        <v>219</v>
+      </c>
+      <c r="E183" s="2" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A184" s="3">
-        <v>60449</v>
+        <v>66668</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C184" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D184" s="3" t="s">
-        <v>55</v>
+        <v>465</v>
+      </c>
+      <c r="C184" s="3" t="s">
+        <v>461</v>
       </c>
       <c r="E184" s="1" t="s">
         <v>522</v>
@@ -5063,16 +5212,16 @@
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A185" s="3">
-        <v>60420</v>
+        <v>66673</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="C185" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D185" s="3" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="E185" s="1" t="s">
         <v>522</v>
@@ -5080,50 +5229,47 @@
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A186" s="3">
-        <v>60084</v>
+        <v>66685</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C186" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D186" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E186" s="1" t="s">
-        <v>522</v>
+        <v>512</v>
+      </c>
+      <c r="C186" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="E186" s="2" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A187" s="3">
-        <v>60194</v>
+        <v>66694</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="C187" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A188" s="3">
-        <v>60402</v>
+        <v>66697</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>62</v>
+        <v>110</v>
       </c>
       <c r="C188" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>63</v>
+        <v>111</v>
       </c>
       <c r="E188" s="1" t="s">
         <v>522</v>
@@ -5131,135 +5277,135 @@
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A189" s="3">
-        <v>60063</v>
+        <v>66700</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E189" s="1" t="s">
-        <v>522</v>
+        <v>189</v>
+      </c>
+      <c r="E189" s="2" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A190" s="3">
-        <v>60401</v>
+        <v>66704</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C190" s="2" t="s">
-        <v>0</v>
+        <v>436</v>
+      </c>
+      <c r="C190" s="3" t="s">
+        <v>170</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E190" s="1" t="s">
-        <v>522</v>
+        <v>217</v>
+      </c>
+      <c r="E190" s="2" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A191" s="3">
-        <v>60409</v>
+        <v>66705</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>68</v>
+        <v>343</v>
       </c>
       <c r="C191" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E191" s="1" t="s">
-        <v>522</v>
+        <v>179</v>
+      </c>
+      <c r="E191" s="2" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A192" s="3">
-        <v>60394</v>
+        <v>66708</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="C192" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="E192" s="1" t="s">
-        <v>522</v>
+        <v>15</v>
+      </c>
+      <c r="E192" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A193" s="3">
-        <v>66726</v>
+        <v>66715</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>72</v>
+        <v>286</v>
       </c>
       <c r="C193" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="E193" s="1" t="s">
-        <v>522</v>
+        <v>287</v>
+      </c>
+      <c r="E193" s="2" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A194" s="3">
-        <v>60447</v>
+        <v>66720</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C194" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D194" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E194" s="1" t="s">
-        <v>522</v>
+        <v>475</v>
+      </c>
+      <c r="C194" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="D194" s="3">
+        <v>678874714</v>
+      </c>
+      <c r="E194" s="2" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A195" s="3">
-        <v>60356</v>
+        <v>66722</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C195" s="2" t="s">
-        <v>0</v>
+        <v>446</v>
+      </c>
+      <c r="C195" s="3" t="s">
+        <v>170</v>
       </c>
       <c r="D195" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E195" s="1" t="s">
-        <v>522</v>
+        <v>225</v>
+      </c>
+      <c r="E195" s="2" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A196" s="3">
-        <v>60001</v>
+        <v>66726</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C196" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="E196" s="1" t="s">
         <v>522</v>
@@ -5267,50 +5413,47 @@
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A197" s="3">
-        <v>60248</v>
+        <v>66730</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C197" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D197" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="E197" s="1" t="s">
-        <v>522</v>
+        <v>445</v>
+      </c>
+      <c r="C197" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="E197" s="2" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A198" s="3">
-        <v>66660</v>
+        <v>66731</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>82</v>
+        <v>279</v>
       </c>
       <c r="C198" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="E198" s="1" t="s">
-        <v>522</v>
+        <v>280</v>
+      </c>
+      <c r="E198" s="2" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A199" s="3">
-        <v>66673</v>
+        <v>66733</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="C199" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="E199" s="1" t="s">
         <v>522</v>
@@ -5318,67 +5461,64 @@
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A200" s="3">
-        <v>66759</v>
+        <v>66735</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>86</v>
+        <v>324</v>
       </c>
       <c r="C200" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="E200" s="1" t="s">
-        <v>522</v>
+        <v>162</v>
+      </c>
+      <c r="E200" s="2" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A201" s="3">
-        <v>66642</v>
+        <v>66738</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C201" s="2" t="s">
-        <v>0</v>
+        <v>464</v>
+      </c>
+      <c r="C201" s="3" t="s">
+        <v>461</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="E201" s="1" t="s">
-        <v>522</v>
+        <v>236</v>
+      </c>
+      <c r="E201" s="4" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A202" s="3">
-        <v>66622</v>
+        <v>66739</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C202" s="2" t="s">
-        <v>0</v>
+        <v>466</v>
+      </c>
+      <c r="C202" s="3" t="s">
+        <v>461</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="E202" s="1" t="s">
-        <v>522</v>
+        <v>238</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A203" s="3">
-        <v>66733</v>
+        <v>66741</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="C203" s="2" t="s">
-        <v>0</v>
+        <v>462</v>
+      </c>
+      <c r="C203" s="3" t="s">
+        <v>461</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>93</v>
+        <v>234</v>
       </c>
       <c r="E203" s="1" t="s">
         <v>522</v>
@@ -5386,33 +5526,33 @@
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A204" s="3">
-        <v>66467</v>
+        <v>66742</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C204" s="2" t="s">
-        <v>0</v>
+        <v>463</v>
+      </c>
+      <c r="C204" s="3" t="s">
+        <v>461</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="E204" s="1" t="s">
-        <v>522</v>
+        <v>235</v>
+      </c>
+      <c r="E204" s="4" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A205" s="3">
-        <v>66620</v>
+        <v>66744</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>96</v>
+        <v>124</v>
       </c>
       <c r="C205" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>97</v>
+        <v>125</v>
       </c>
       <c r="E205" s="1" t="s">
         <v>522</v>
@@ -5420,101 +5560,98 @@
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A206" s="3">
-        <v>60410</v>
+        <v>66745</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C206" s="2" t="s">
-        <v>0</v>
+        <v>453</v>
+      </c>
+      <c r="C206" s="3" t="s">
+        <v>517</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="E206" s="1" t="s">
-        <v>522</v>
+        <v>231</v>
+      </c>
+      <c r="E206" s="2" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A207" s="3">
-        <v>60025</v>
+        <v>66748</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>100</v>
+        <v>341</v>
       </c>
       <c r="C207" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="E207" s="1" t="s">
-        <v>522</v>
+        <v>177</v>
+      </c>
+      <c r="E207" s="2" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A208" s="3">
-        <v>60407</v>
+        <v>66749</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>102</v>
+        <v>288</v>
       </c>
       <c r="C208" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E208" s="1" t="s">
-        <v>522</v>
+        <v>289</v>
+      </c>
+      <c r="E208" s="2" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A209" s="3">
-        <v>60415</v>
+        <v>66750</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="C209" s="2" t="s">
-        <v>0</v>
+        <v>495</v>
+      </c>
+      <c r="C209" s="3" t="s">
+        <v>492</v>
       </c>
       <c r="D209" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="E209" s="1" t="s">
-        <v>522</v>
+        <v>259</v>
+      </c>
+      <c r="E209" s="2" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A210" s="3">
-        <v>66753</v>
+        <v>66751</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="C210" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D210" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="E210" s="1" t="s">
-        <v>522</v>
+        <v>393</v>
+      </c>
+      <c r="C210" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="E210" s="2" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A211" s="3">
-        <v>60303</v>
+        <v>66753</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C211" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D211" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E211" s="1" t="s">
         <v>522</v>
@@ -5522,16 +5659,16 @@
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A212" s="3">
-        <v>66697</v>
+        <v>66755</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C212" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D212" s="3" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E212" s="1" t="s">
         <v>522</v>
@@ -5539,33 +5676,33 @@
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A213" s="3">
-        <v>60023</v>
+        <v>66756</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>112</v>
+        <v>290</v>
       </c>
       <c r="C213" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D213" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="E213" s="1" t="s">
-        <v>522</v>
+        <v>291</v>
+      </c>
+      <c r="E213" s="2" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A214" s="3">
-        <v>66755</v>
+        <v>66757</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>114</v>
+        <v>42</v>
       </c>
       <c r="C214" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>115</v>
+        <v>43</v>
       </c>
       <c r="E214" s="1" t="s">
         <v>522</v>
@@ -5573,33 +5710,33 @@
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A215" s="3">
-        <v>66778</v>
+        <v>66758</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C215" s="2" t="s">
-        <v>0</v>
+        <v>494</v>
+      </c>
+      <c r="C215" s="3" t="s">
+        <v>492</v>
       </c>
       <c r="D215" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="E215" s="1" t="s">
-        <v>522</v>
+        <v>258</v>
+      </c>
+      <c r="E215" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A216" s="3">
-        <v>60450</v>
+        <v>66759</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="C216" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>119</v>
+        <v>87</v>
       </c>
       <c r="E216" s="1" t="s">
         <v>522</v>
@@ -5607,945 +5744,853 @@
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A217" s="3">
-        <v>66780</v>
+        <v>66768</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="C217" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D217" s="3" t="s">
-        <v>121</v>
+        <v>31</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A218" s="3">
-        <v>60009</v>
+        <v>66770</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C218" s="2" t="s">
-        <v>0</v>
+        <v>490</v>
+      </c>
+      <c r="C218" t="s">
+        <v>519</v>
       </c>
       <c r="D218" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E218" s="1" t="s">
-        <v>522</v>
+        <v>255</v>
+      </c>
+      <c r="E218" s="2" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A219" s="3">
-        <v>66744</v>
+        <v>66772</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>124</v>
+        <v>17</v>
       </c>
       <c r="C219" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D219" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="E219" s="1" t="s">
-        <v>522</v>
+        <v>18</v>
+      </c>
+      <c r="E219" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A220" s="3">
-        <v>66777</v>
+        <v>66773</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>126</v>
+        <v>34</v>
       </c>
       <c r="C220" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>125</v>
+        <v>35</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A221" s="3">
-        <v>66798</v>
+        <v>66774</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>127</v>
+        <v>20</v>
       </c>
       <c r="C221" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D221" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E221" s="1" t="s">
-        <v>522</v>
+      <c r="E221" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A222" s="3">
-        <v>66801</v>
-      </c>
-      <c r="B222" s="2" t="s">
-        <v>129</v>
+        <v>66775</v>
+      </c>
+      <c r="B222" s="3" t="s">
+        <v>292</v>
       </c>
       <c r="C222" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D222" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="E222" s="1" t="s">
-        <v>522</v>
+      <c r="D222" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="E222" s="2" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A223" s="3">
-        <v>66808</v>
+        <v>66776</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>131</v>
+        <v>345</v>
       </c>
       <c r="C223" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D223" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="E223" s="1" t="s">
-        <v>522</v>
+        <v>181</v>
+      </c>
+      <c r="E223" s="2" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A224" s="3">
-        <v>66809</v>
+        <v>66777</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="C224" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D224" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="E224" s="1" t="s">
-        <v>522</v>
+        <v>125</v>
+      </c>
+      <c r="E224" s="2" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A225" s="3">
-        <v>66810</v>
+        <v>66777</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="C225" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D225" s="3" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="E225" s="1" t="s">
         <v>522</v>
       </c>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A226" s="3">
+        <v>66778</v>
+      </c>
       <c r="B226" s="3" t="s">
-        <v>272</v>
+        <v>116</v>
       </c>
       <c r="C226" s="2" t="s">
         <v>0</v>
+      </c>
+      <c r="D226" s="3" t="s">
+        <v>117</v>
       </c>
       <c r="E226" s="1" t="s">
         <v>522</v>
       </c>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A227" s="3"/>
+      <c r="A227" s="3">
+        <v>66779</v>
+      </c>
       <c r="B227" s="3" t="s">
-        <v>413</v>
+        <v>467</v>
       </c>
       <c r="C227" s="3" t="s">
-        <v>170</v>
+        <v>461</v>
       </c>
       <c r="D227" s="3" t="s">
-        <v>414</v>
+        <v>125</v>
       </c>
       <c r="E227" s="2" t="s">
-        <v>206</v>
+        <v>138</v>
       </c>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A228" s="3">
+        <v>66780</v>
+      </c>
       <c r="B228" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="C228" s="3" t="s">
-        <v>458</v>
-      </c>
-      <c r="E228" s="2" t="s">
-        <v>138</v>
+        <v>120</v>
+      </c>
+      <c r="C228" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D228" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E228" s="1" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A229" s="3">
+        <v>66785</v>
+      </c>
       <c r="B229" s="3" t="s">
-        <v>459</v>
-      </c>
-      <c r="C229" s="3" t="s">
-        <v>458</v>
-      </c>
-      <c r="D229" s="3">
-        <v>677255778</v>
+        <v>19</v>
+      </c>
+      <c r="C229" s="2" t="s">
+        <v>0</v>
       </c>
       <c r="E229" s="2" t="s">
-        <v>138</v>
+        <v>1</v>
       </c>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A230" s="3">
-        <v>66504</v>
+        <v>66786</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>460</v>
-      </c>
-      <c r="C230" s="3" t="s">
-        <v>461</v>
+        <v>480</v>
+      </c>
+      <c r="C230" t="s">
+        <v>240</v>
       </c>
       <c r="D230" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="E230" s="1" t="s">
-        <v>522</v>
+        <v>247</v>
+      </c>
+      <c r="E230" s="2" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A231" s="3">
-        <v>66741</v>
+        <v>66793</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>462</v>
-      </c>
-      <c r="C231" s="3" t="s">
-        <v>461</v>
+        <v>316</v>
+      </c>
+      <c r="C231" s="2" t="s">
+        <v>0</v>
       </c>
       <c r="D231" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="E231" s="1" t="s">
-        <v>522</v>
+        <v>159</v>
+      </c>
+      <c r="E231" s="2" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A232" s="3">
-        <v>66742</v>
+        <v>66794</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>463</v>
-      </c>
-      <c r="C232" s="3" t="s">
-        <v>461</v>
+        <v>346</v>
+      </c>
+      <c r="C232" s="2" t="s">
+        <v>0</v>
       </c>
       <c r="D232" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="E232" s="4" t="s">
-        <v>209</v>
+        <v>182</v>
+      </c>
+      <c r="E232" s="2" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A233" s="3">
-        <v>66738</v>
+        <v>66798</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>464</v>
-      </c>
-      <c r="C233" s="3" t="s">
-        <v>461</v>
+        <v>127</v>
+      </c>
+      <c r="C233" s="2" t="s">
+        <v>0</v>
       </c>
       <c r="D233" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="E233" s="4" t="s">
-        <v>209</v>
+        <v>128</v>
+      </c>
+      <c r="E233" s="1" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A234" s="3">
-        <v>66668</v>
+        <v>66799</v>
       </c>
       <c r="B234" s="3" t="s">
-        <v>465</v>
-      </c>
-      <c r="C234" s="3" t="s">
-        <v>461</v>
+        <v>36</v>
+      </c>
+      <c r="C234" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D234" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A235" s="3">
-        <v>62039</v>
+        <v>66800</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="C235" s="3" t="s">
-        <v>461</v>
+        <v>317</v>
+      </c>
+      <c r="C235" s="2" t="s">
+        <v>0</v>
       </c>
       <c r="D235" s="3" t="s">
-        <v>237</v>
+        <v>160</v>
+      </c>
+      <c r="E235" s="2" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A236" s="3">
-        <v>66739</v>
-      </c>
-      <c r="B236" s="3" t="s">
-        <v>466</v>
-      </c>
-      <c r="C236" s="3" t="s">
-        <v>461</v>
-      </c>
-      <c r="D236" s="3" t="s">
-        <v>238</v>
+        <v>66801</v>
+      </c>
+      <c r="B236" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C236" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D236" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E236" s="1" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A237" s="3">
-        <v>66779</v>
+        <v>66802</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="C237" s="3" t="s">
-        <v>461</v>
+        <v>347</v>
+      </c>
+      <c r="C237" s="2" t="s">
+        <v>0</v>
       </c>
       <c r="D237" s="3" t="s">
-        <v>125</v>
+        <v>183</v>
       </c>
       <c r="E237" s="2" t="s">
-        <v>138</v>
+        <v>212</v>
       </c>
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A238" s="3">
+        <v>66803</v>
+      </c>
       <c r="B238" s="3" t="s">
-        <v>468</v>
+        <v>504</v>
       </c>
       <c r="C238" s="3" t="s">
-        <v>461</v>
+        <v>505</v>
       </c>
       <c r="D238" s="3" t="s">
-        <v>239</v>
+        <v>268</v>
       </c>
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A239" s="3">
-        <v>66513</v>
+        <v>66805</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>469</v>
+        <v>203</v>
       </c>
       <c r="C239" s="3" t="s">
-        <v>470</v>
-      </c>
-      <c r="D239" s="3" t="s">
-        <v>471</v>
+        <v>170</v>
       </c>
       <c r="E239" s="2" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A240" s="3">
+        <v>66806</v>
+      </c>
       <c r="B240" s="3" t="s">
-        <v>472</v>
+        <v>454</v>
       </c>
       <c r="C240" s="3" t="s">
-        <v>470</v>
-      </c>
-      <c r="D240" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="E240" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="E240" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A241" s="3">
+        <v>66808</v>
+      </c>
+      <c r="B241" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C241" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D241" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E241" s="1" t="s">
         <v>522</v>
-      </c>
-    </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B241" s="3" t="s">
-        <v>473</v>
-      </c>
-      <c r="C241" s="3" t="s">
-        <v>470</v>
-      </c>
-      <c r="D241" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="E241" s="2" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A242" s="3">
-        <v>60991</v>
+        <v>66809</v>
       </c>
       <c r="B242" s="3" t="s">
-        <v>474</v>
-      </c>
-      <c r="C242" s="3" t="s">
-        <v>518</v>
-      </c>
-      <c r="D242" s="3">
-        <v>695475025</v>
-      </c>
-      <c r="E242" s="2" t="s">
-        <v>137</v>
+        <v>133</v>
+      </c>
+      <c r="C242" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D242" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E242" s="1" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A243" s="3">
-        <v>66720</v>
+        <v>66810</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>475</v>
-      </c>
-      <c r="C243" s="3" t="s">
-        <v>518</v>
-      </c>
-      <c r="D243" s="3">
-        <v>678874714</v>
-      </c>
-      <c r="E243" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
+      </c>
+      <c r="C243" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D243" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E243" s="1" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A244" s="3">
-        <v>66564</v>
-      </c>
       <c r="B244" s="3" t="s">
-        <v>476</v>
+        <v>450</v>
       </c>
       <c r="C244" s="3" t="s">
-        <v>518</v>
+        <v>170</v>
+      </c>
+      <c r="D244" s="3" t="s">
+        <v>229</v>
       </c>
       <c r="E244" s="2" t="s">
-        <v>349</v>
+        <v>212</v>
       </c>
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A245" s="3">
-        <v>60127</v>
-      </c>
       <c r="B245" s="3" t="s">
-        <v>477</v>
-      </c>
-      <c r="C245" t="s">
-        <v>240</v>
-      </c>
-      <c r="D245" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="E245" s="2" t="s">
-        <v>137</v>
+        <v>210</v>
+      </c>
+      <c r="C245" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="E245" s="4" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A246" s="3">
-        <v>60992</v>
-      </c>
       <c r="B246" s="3" t="s">
-        <v>478</v>
-      </c>
-      <c r="C246" t="s">
-        <v>240</v>
-      </c>
-      <c r="E246" s="2" t="s">
-        <v>137</v>
+        <v>272</v>
+      </c>
+      <c r="C246" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E246" s="1" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B247" s="3" t="s">
-        <v>479</v>
-      </c>
-      <c r="C247" t="s">
-        <v>240</v>
+        <v>448</v>
+      </c>
+      <c r="C247" s="3" t="s">
+        <v>170</v>
       </c>
       <c r="D247" s="3" t="s">
-        <v>246</v>
+        <v>227</v>
       </c>
       <c r="E247" s="2" t="s">
-        <v>137</v>
+        <v>212</v>
       </c>
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A248" s="3">
-        <v>66786</v>
-      </c>
       <c r="B248" s="3" t="s">
-        <v>480</v>
-      </c>
-      <c r="C248" t="s">
-        <v>240</v>
+        <v>295</v>
+      </c>
+      <c r="C248" s="2" t="s">
+        <v>0</v>
       </c>
       <c r="D248" s="3" t="s">
-        <v>247</v>
+        <v>140</v>
       </c>
       <c r="E248" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A249" s="3">
-        <v>63043</v>
-      </c>
+      <c r="A249" s="3"/>
       <c r="B249" s="3" t="s">
-        <v>481</v>
-      </c>
-      <c r="C249" t="s">
-        <v>240</v>
+        <v>413</v>
+      </c>
+      <c r="C249" s="3" t="s">
+        <v>170</v>
       </c>
       <c r="D249" s="3" t="s">
-        <v>248</v>
+        <v>414</v>
       </c>
       <c r="E249" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B250" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="C250" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E250" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B251" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="C251" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="D251" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B252" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="C252" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="E252" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A253" s="3"/>
+      <c r="B253" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="C253" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D253" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E253" s="2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B254" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="C254" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="E254" s="2" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A250" s="3">
-        <v>66518</v>
-      </c>
-      <c r="B250" s="3" t="s">
-        <v>482</v>
-      </c>
-      <c r="C250" t="s">
-        <v>240</v>
-      </c>
-      <c r="D250" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="E250" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A251" s="3">
-        <v>61100</v>
-      </c>
-      <c r="B251" s="3" t="s">
-        <v>483</v>
-      </c>
-      <c r="C251" t="s">
-        <v>240</v>
-      </c>
-      <c r="D251" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="E251" s="2" t="s">
+    <row r="255" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B255" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="C255" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="E255" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B256" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="C256" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="D256" s="3">
+        <v>677255778</v>
+      </c>
+      <c r="E256" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="257" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B257" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="C257" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="D257" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="E257" s="2" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A252" s="3">
-        <v>60028</v>
-      </c>
-      <c r="B252" s="3" t="s">
-        <v>484</v>
-      </c>
-      <c r="C252" t="s">
-        <v>240</v>
-      </c>
-      <c r="D252" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="E252" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A253" s="3">
-        <v>60980</v>
-      </c>
-      <c r="B253" s="3" t="s">
-        <v>485</v>
-      </c>
-      <c r="C253" t="s">
-        <v>240</v>
-      </c>
-      <c r="D253" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="E253" s="2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A254" s="3">
-        <v>62153</v>
-      </c>
-      <c r="B254" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="C254" t="s">
-        <v>240</v>
-      </c>
-      <c r="D254" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="E254" s="2" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A255" s="3">
-        <v>66664</v>
-      </c>
-      <c r="B255" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="C255" t="s">
-        <v>240</v>
-      </c>
-      <c r="D255" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="E255" s="2" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A256" s="3">
-        <v>60430</v>
-      </c>
-      <c r="B256" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="C256" t="s">
-        <v>519</v>
-      </c>
-      <c r="E256" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A257" s="3">
-        <v>60983</v>
-      </c>
-      <c r="B257" s="3" t="s">
-        <v>488</v>
-      </c>
-      <c r="C257" t="s">
-        <v>519</v>
-      </c>
-      <c r="D257" s="3">
-        <v>699101960</v>
-      </c>
-      <c r="E257" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A258" s="3">
-        <v>62129</v>
-      </c>
+    <row r="258" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B258" s="3" t="s">
-        <v>489</v>
-      </c>
-      <c r="C258" t="s">
-        <v>519</v>
+        <v>371</v>
+      </c>
+      <c r="C258" s="2" t="s">
+        <v>0</v>
       </c>
       <c r="E258" s="2" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A259" s="3">
-        <v>66631</v>
-      </c>
+    <row r="259" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B259" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="C259" t="s">
-        <v>519</v>
+        <v>449</v>
+      </c>
+      <c r="C259" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="D259" s="3" t="s">
+        <v>228</v>
       </c>
       <c r="E259" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="260" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B260" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="C260" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E260" s="2" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A260" s="3">
-        <v>66770</v>
-      </c>
-      <c r="B260" s="3" t="s">
-        <v>490</v>
-      </c>
-      <c r="C260" t="s">
-        <v>519</v>
-      </c>
-      <c r="D260" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="E260" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A261" s="3">
-        <v>61101</v>
-      </c>
+    <row r="261" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B261" s="3" t="s">
-        <v>491</v>
+        <v>452</v>
       </c>
       <c r="C261" s="3" t="s">
-        <v>492</v>
+        <v>170</v>
       </c>
       <c r="D261" s="3" t="s">
-        <v>256</v>
+        <v>230</v>
       </c>
       <c r="E261" s="2" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A262" s="3">
-        <v>60501</v>
-      </c>
+    <row r="262" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B262" s="3" t="s">
-        <v>493</v>
+        <v>515</v>
       </c>
       <c r="C262" s="3" t="s">
-        <v>492</v>
+        <v>270</v>
       </c>
       <c r="D262" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="E262" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A263" s="3">
-        <v>66758</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="E262" s="2" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="263" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B263" s="3" t="s">
-        <v>494</v>
+        <v>506</v>
       </c>
       <c r="C263" s="3" t="s">
-        <v>492</v>
-      </c>
-      <c r="D263" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="E263" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A264" s="3">
-        <v>66750</v>
-      </c>
+        <v>507</v>
+      </c>
+      <c r="E263" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="264" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B264" s="3" t="s">
-        <v>495</v>
+        <v>457</v>
       </c>
       <c r="C264" s="3" t="s">
-        <v>492</v>
-      </c>
-      <c r="D264" s="3" t="s">
-        <v>259</v>
+        <v>458</v>
       </c>
       <c r="E264" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="265" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B265" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="C265" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="D265" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="E265" s="2" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A265" s="3">
-        <v>60975</v>
-      </c>
-      <c r="B265" s="3" t="s">
-        <v>496</v>
-      </c>
-      <c r="C265" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="D265" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="E265" s="2" t="s">
+    <row r="266" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B266" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="C266" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="E266" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="267" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B267" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C267" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E267" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="268" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B268" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="C268" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="E268" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="269" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B269" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="C269" t="s">
+        <v>240</v>
+      </c>
+      <c r="D269" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="E269" s="2" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A266" s="3">
-        <v>60315</v>
-      </c>
-      <c r="B266" s="3" t="s">
-        <v>497</v>
-      </c>
-      <c r="C266" s="3" t="s">
-        <v>505</v>
-      </c>
-      <c r="D266" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="E266" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A267" s="3">
-        <v>60361</v>
-      </c>
-      <c r="B267" s="3" t="s">
-        <v>498</v>
-      </c>
-      <c r="C267" s="3" t="s">
-        <v>505</v>
-      </c>
-      <c r="D267" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="E267" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A268" s="3">
-        <v>60365</v>
-      </c>
-      <c r="B268" s="3" t="s">
-        <v>499</v>
-      </c>
-      <c r="C268" s="3" t="s">
-        <v>505</v>
-      </c>
-      <c r="D268" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="E268" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A269" s="3">
-        <v>61122</v>
-      </c>
-      <c r="B269" s="3" t="s">
-        <v>500</v>
-      </c>
-      <c r="C269" s="3" t="s">
-        <v>505</v>
-      </c>
-      <c r="D269" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="E269" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A270" s="3">
-        <v>62154</v>
-      </c>
+    <row r="270" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B270" s="3" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="C270" s="3" t="s">
-        <v>505</v>
+        <v>461</v>
       </c>
       <c r="D270" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="E270" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="271" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B271" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="C271" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E271" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="272" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B272" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="C272" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E272" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B273" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="C273" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="D273" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="E273" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B274" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C274" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E274" s="2" t="s">
         <v>349</v>
-      </c>
-    </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A271" s="3">
-        <v>66629</v>
-      </c>
-      <c r="B271" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="C271" s="3" t="s">
-        <v>505</v>
-      </c>
-      <c r="D271" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="E271" s="2" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A272" s="3">
-        <v>62039</v>
-      </c>
-      <c r="B272" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="C272" s="3" t="s">
-        <v>505</v>
-      </c>
-      <c r="D272" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="E272" s="2" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A273" s="3">
-        <v>63053</v>
-      </c>
-      <c r="B273" s="3" t="s">
-        <v>503</v>
-      </c>
-      <c r="C273" s="3" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A274" s="3">
-        <v>66803</v>
-      </c>
-      <c r="B274" s="3" t="s">
-        <v>504</v>
-      </c>
-      <c r="C274" s="3" t="s">
-        <v>505</v>
-      </c>
-      <c r="D274" s="3" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B275" s="3" t="s">
-        <v>506</v>
+        <v>472</v>
       </c>
       <c r="C275" s="3" t="s">
-        <v>507</v>
-      </c>
-      <c r="E275" s="2" t="s">
-        <v>138</v>
+        <v>470</v>
+      </c>
+      <c r="D275" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="E275" s="1" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B276" s="3" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="C276" s="3" t="s">
-        <v>509</v>
-      </c>
-      <c r="D276" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
+      </c>
+      <c r="E276" s="2" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.2">
@@ -6560,64 +6605,69 @@
       </c>
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A278" s="3">
-        <v>66685</v>
-      </c>
       <c r="B278" s="3" t="s">
-        <v>512</v>
+        <v>399</v>
       </c>
       <c r="C278" s="3" t="s">
-        <v>270</v>
+        <v>170</v>
       </c>
       <c r="E278" s="2" t="s">
-        <v>137</v>
+        <v>205</v>
       </c>
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B279" s="3" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="C279" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="E279" s="2" t="s">
-        <v>138</v>
+      <c r="E279" s="1" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B280" s="3" t="s">
-        <v>514</v>
-      </c>
-      <c r="C280" s="3" t="s">
-        <v>270</v>
+        <v>369</v>
+      </c>
+      <c r="C280" s="2" t="s">
+        <v>0</v>
       </c>
       <c r="E280" s="2" t="s">
-        <v>212</v>
+        <v>349</v>
       </c>
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B281" s="3" t="s">
-        <v>515</v>
+        <v>211</v>
       </c>
       <c r="C281" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="D281" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="E281" s="2" t="s">
-        <v>349</v>
+        <v>170</v>
+      </c>
+      <c r="E281" s="4" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B282" s="3" t="s">
-        <v>516</v>
-      </c>
-      <c r="C282" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="E282" s="1" t="s">
-        <v>522</v>
+        <v>367</v>
+      </c>
+      <c r="C282" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E282" s="2" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A283" t="s">
+        <v>525</v>
+      </c>
+      <c r="B283" s="3"/>
+      <c r="C283" s="3"/>
+      <c r="E283">
+        <f>SUBTOTAL(103,presta_soins[TYPE])</f>
+        <v>274</v>
       </c>
     </row>
   </sheetData>

--- a/chanas/presta/media/prestataire_soins2.xlsx
+++ b/chanas/presta/media/prestataire_soins2.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/antboy/Desktop/PWC/CODE/venv/chanas_2/chanas/presta/media/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F82F244A-637C-6D4D-95CD-0236A0AED75A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D67D925-81E2-A24B-A5AD-481284FAE488}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{DAEB2858-4AB9-DC42-BCCA-AA77F40B5715}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,14 +36,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1063" uniqueCount="526">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1070" uniqueCount="525">
   <si>
     <t>DOUALA </t>
   </si>
   <si>
-    <t>HOPITAUX PUBLICS </t>
-  </si>
-  <si>
     <t>CODE</t>
   </si>
   <si>
@@ -449,15 +446,6 @@
     <t>677 135 935</t>
   </si>
   <si>
-    <t>HOPITAUX PUBLICS</t>
-  </si>
-  <si>
-    <t>HOPITAUX CONFESSIONNELS</t>
-  </si>
-  <si>
-    <t>CABINETS DENTAIRES</t>
-  </si>
-  <si>
     <t>657 341 168</t>
   </si>
   <si>
@@ -650,9 +638,6 @@
     <t>HOPITAL DE ZALOM FOND. AD. LUCEM</t>
   </si>
   <si>
-    <t>CLINIQUES PRIVEES</t>
-  </si>
-  <si>
     <t>OPHTALMOLOGUES</t>
   </si>
   <si>
@@ -665,18 +650,12 @@
     <t>CABINET DENTAIRE DE BASTOS</t>
   </si>
   <si>
-    <t>LABORATOIRES &amp; IMAGERIES</t>
-  </si>
-  <si>
     <t>BIO DIAGNOSTICA</t>
   </si>
   <si>
     <t>SAS KABIOMED</t>
   </si>
   <si>
-    <t>PHARMACIES</t>
-  </si>
-  <si>
     <t>658 104 732</t>
   </si>
   <si>
@@ -953,9 +932,6 @@
     <t>CENTRE MEDICAL D'OPHTALMOLOGIE Ste THERESE</t>
   </si>
   <si>
-    <t>LABORATOIRES</t>
-  </si>
-  <si>
     <t>LABO LOUIS PASTEUR</t>
   </si>
   <si>
@@ -1085,9 +1061,6 @@
     <t>PHARMACIE CONCORDE</t>
   </si>
   <si>
-    <t>OPTICIENS</t>
-  </si>
-  <si>
     <t>PRISM OPTIQUE</t>
   </si>
   <si>
@@ -1596,21 +1569,6 @@
   </si>
   <si>
     <t>MAROUA</t>
-  </si>
-  <si>
-    <r>
-      <t> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t>HOPITAUX CONFESSIONNELS </t>
-    </r>
   </si>
   <si>
     <r>
@@ -1628,21 +1586,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <t> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t>CLINIQUES &amp; POLYCLINIQUES</t>
-    </r>
-  </si>
-  <si>
     <t>FOUNDATION</t>
   </si>
   <si>
@@ -1650,6 +1593,36 @@
   </si>
   <si>
     <t>Total</t>
+  </si>
+  <si>
+    <t> CLINIQUE &amp; POLYCLINIQUE</t>
+  </si>
+  <si>
+    <t>OPTICIEN</t>
+  </si>
+  <si>
+    <t>HOPITAL PUBLIC </t>
+  </si>
+  <si>
+    <t>HOPITAL PUBLIC</t>
+  </si>
+  <si>
+    <t> HOPITAL CONFESSIONNEL </t>
+  </si>
+  <si>
+    <t>HOPITAL CONFESSIONNEL</t>
+  </si>
+  <si>
+    <t>CLINIQUE PRIVEE</t>
+  </si>
+  <si>
+    <t>PHARMACIE</t>
+  </si>
+  <si>
+    <t>LABORATOIRE</t>
+  </si>
+  <si>
+    <t>LABORATOIRE &amp; IMAGERIES</t>
   </si>
 </sst>
 </file>
@@ -1760,7 +1733,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
@@ -1796,7 +1769,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
+        <b/>
         <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
@@ -1826,15 +1799,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0F51D3D8-888E-1F4D-8383-2294D5BEA7E8}" name="presta_soins" displayName="presta_soins" ref="A1:E283" totalsRowCount="1" headerRowDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0F51D3D8-888E-1F4D-8383-2294D5BEA7E8}" name="presta_soins" displayName="presta_soins" ref="A1:E283" totalsRowCount="1" headerRowDxfId="4">
   <autoFilter ref="A1:E282" xr:uid="{0F51D3D8-888E-1F4D-8383-2294D5BEA7E8}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E282">
-    <sortCondition ref="A1:A282"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E273">
+    <sortCondition ref="A1:A273"/>
   </sortState>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{349BB440-2E5D-2843-AA4B-FAD92399387E}" name="CODE" totalsRowLabel="Total"/>
-    <tableColumn id="2" xr3:uid="{2622A07C-27E5-7342-A004-FC36A3C08F04}" name="PRESTATAIRES" dataDxfId="4" totalsRowDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{0513F6E7-602A-ED46-8CFE-B9790B9A6BD2}" name="LIEU" dataDxfId="3" totalsRowDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{2622A07C-27E5-7342-A004-FC36A3C08F04}" name="PRESTATAIRES" dataDxfId="3" totalsRowDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{0513F6E7-602A-ED46-8CFE-B9790B9A6BD2}" name="LIEU" dataDxfId="2" totalsRowDxfId="0"/>
     <tableColumn id="4" xr3:uid="{7CD384D9-9904-2640-B4D9-D31547083864}" name="TELEPHONE"/>
     <tableColumn id="5" xr3:uid="{DFD4B9DD-90BB-F949-8950-AACF1FD0E6AD}" name="TYPE" totalsRowFunction="count"/>
   </tableColumns>
@@ -2159,7 +2132,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E61D2BEC-D9B7-554D-8FA8-A40B60534B70}">
-  <dimension ref="A1:E283"/>
+  <dimension ref="A1:E297"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -2171,19 +2144,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>5</v>
-      </c>
       <c r="E1" s="2" t="s">
-        <v>524</v>
+        <v>513</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
@@ -2191,16 +2164,16 @@
         <v>60001</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>79</v>
-      </c>
       <c r="E2" s="1" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -2208,16 +2181,16 @@
         <v>60009</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>123</v>
-      </c>
       <c r="E3" s="1" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -2225,16 +2198,16 @@
         <v>60023</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>113</v>
-      </c>
       <c r="E4" s="1" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
@@ -2242,16 +2215,16 @@
         <v>60023</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>305</v>
+        <v>523</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
@@ -2259,16 +2232,16 @@
         <v>60025</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>101</v>
-      </c>
       <c r="E6" s="1" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
@@ -2276,13 +2249,13 @@
         <v>60027</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1</v>
+        <v>517</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
@@ -2290,16 +2263,16 @@
         <v>60028</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
       <c r="C8" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
@@ -2307,16 +2280,16 @@
         <v>60029</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>39</v>
-      </c>
       <c r="E9" s="1" t="s">
-        <v>521</v>
+        <v>511</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
@@ -2324,13 +2297,13 @@
         <v>60030</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>137</v>
+        <v>518</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
@@ -2338,16 +2311,16 @@
         <v>60036</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>137</v>
+        <v>518</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
@@ -2355,16 +2328,16 @@
         <v>60037</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>137</v>
+        <v>518</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
@@ -2372,16 +2345,16 @@
         <v>60063</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>65</v>
-      </c>
       <c r="E13" s="1" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
@@ -2389,16 +2362,16 @@
         <v>60084</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="E14" s="1" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
@@ -2406,16 +2379,16 @@
         <v>60107</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>455</v>
+        <v>446</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>517</v>
+        <v>508</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
@@ -2423,16 +2396,16 @@
         <v>60116</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>137</v>
+        <v>518</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
@@ -2440,16 +2413,16 @@
         <v>60118</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="E17" s="2" t="s">
-        <v>1</v>
+        <v>517</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
@@ -2457,16 +2430,16 @@
         <v>60127</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>477</v>
+        <v>468</v>
       </c>
       <c r="C18" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>137</v>
+        <v>518</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
@@ -2474,16 +2447,16 @@
         <v>60194</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>61</v>
-      </c>
       <c r="E19" s="1" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
@@ -2491,16 +2464,16 @@
         <v>60198</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>204</v>
+        <v>521</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
@@ -2508,16 +2481,16 @@
         <v>60208</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>33</v>
-      </c>
       <c r="E21" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
@@ -2525,16 +2498,16 @@
         <v>60246</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
@@ -2542,16 +2515,16 @@
         <v>60248</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>81</v>
-      </c>
       <c r="E23" s="1" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
@@ -2559,16 +2532,16 @@
         <v>60258</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
@@ -2576,16 +2549,16 @@
         <v>60299</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>25</v>
-      </c>
       <c r="E25" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
@@ -2593,16 +2566,16 @@
         <v>60303</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>109</v>
-      </c>
       <c r="E26" s="1" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
@@ -2610,16 +2583,16 @@
         <v>60308</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
@@ -2627,16 +2600,16 @@
         <v>60313</v>
       </c>
       <c r="B28" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>27</v>
-      </c>
       <c r="E28" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
@@ -2644,16 +2617,16 @@
         <v>60315</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>497</v>
+        <v>488</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>137</v>
+        <v>518</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
@@ -2661,13 +2634,13 @@
         <v>60335</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>0</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>1</v>
+        <v>517</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
@@ -2675,16 +2648,16 @@
         <v>60340</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>349</v>
+        <v>516</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
@@ -2692,16 +2665,16 @@
         <v>60356</v>
       </c>
       <c r="B32" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D32" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C32" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="E32" s="1" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
@@ -2709,16 +2682,16 @@
         <v>60361</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>498</v>
+        <v>489</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
@@ -2726,16 +2699,16 @@
         <v>60365</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
@@ -2743,16 +2716,16 @@
         <v>60385</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
@@ -2760,16 +2733,16 @@
         <v>60394</v>
       </c>
       <c r="B36" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D36" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C36" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>71</v>
-      </c>
       <c r="E36" s="1" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
@@ -2777,16 +2750,16 @@
         <v>60401</v>
       </c>
       <c r="B37" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D37" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C37" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>67</v>
-      </c>
       <c r="E37" s="1" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
@@ -2794,16 +2767,16 @@
         <v>60402</v>
       </c>
       <c r="B38" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D38" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C38" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>63</v>
-      </c>
       <c r="E38" s="1" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
@@ -2811,16 +2784,16 @@
         <v>60403</v>
       </c>
       <c r="B39" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D39" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C39" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="E39" s="1" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
@@ -2828,16 +2801,16 @@
         <v>60406</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
@@ -2845,16 +2818,16 @@
         <v>60407</v>
       </c>
       <c r="B41" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D41" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C41" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>103</v>
-      </c>
       <c r="E41" s="1" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
@@ -2862,16 +2835,16 @@
         <v>60409</v>
       </c>
       <c r="B42" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D42" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C42" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>69</v>
-      </c>
       <c r="E42" s="1" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
@@ -2879,16 +2852,16 @@
         <v>60410</v>
       </c>
       <c r="B43" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D43" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C43" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>99</v>
-      </c>
       <c r="E43" s="1" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
@@ -2896,16 +2869,16 @@
         <v>60414</v>
       </c>
       <c r="B44" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D44" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C44" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="E44" s="1" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
@@ -2913,16 +2886,16 @@
         <v>60415</v>
       </c>
       <c r="B45" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D45" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C45" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>105</v>
-      </c>
       <c r="E45" s="1" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
@@ -2930,16 +2903,16 @@
         <v>60420</v>
       </c>
       <c r="B46" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D46" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C46" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>57</v>
-      </c>
       <c r="E46" s="1" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
@@ -2947,13 +2920,13 @@
         <v>60430</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="C47" t="s">
-        <v>519</v>
+        <v>510</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>137</v>
+        <v>518</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
@@ -2961,16 +2934,16 @@
         <v>60438</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
@@ -2978,16 +2951,16 @@
         <v>60442</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.2">
@@ -2995,16 +2968,16 @@
         <v>60447</v>
       </c>
       <c r="B50" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D50" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C50" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>75</v>
-      </c>
       <c r="E50" s="1" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.2">
@@ -3012,16 +2985,16 @@
         <v>60449</v>
       </c>
       <c r="B51" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D51" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C51" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>55</v>
-      </c>
       <c r="E51" s="1" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.2">
@@ -3029,16 +3002,16 @@
         <v>60450</v>
       </c>
       <c r="B52" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D52" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C52" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>119</v>
-      </c>
       <c r="E52" s="1" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.2">
@@ -3046,16 +3019,16 @@
         <v>60457</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
@@ -3063,16 +3036,16 @@
         <v>60457</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.2">
@@ -3080,16 +3053,16 @@
         <v>60458</v>
       </c>
       <c r="B55" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D55" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C55" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="E55" s="1" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.2">
@@ -3097,16 +3070,16 @@
         <v>60459</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>1</v>
+        <v>517</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.2">
@@ -3114,16 +3087,16 @@
         <v>60481</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.2">
@@ -3131,16 +3104,16 @@
         <v>60501</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>492</v>
+        <v>483</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="E58" t="s">
-        <v>523</v>
+        <v>512</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.2">
@@ -3148,13 +3121,13 @@
         <v>60900</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>137</v>
+        <v>518</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.2">
@@ -3162,16 +3135,16 @@
         <v>60952</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>138</v>
+        <v>520</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.2">
@@ -3179,16 +3152,16 @@
         <v>60975</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>496</v>
+        <v>487</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>137</v>
+        <v>518</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.2">
@@ -3196,16 +3169,16 @@
         <v>60978</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>209</v>
+        <v>524</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.2">
@@ -3213,16 +3186,16 @@
         <v>60980</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="C63" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>138</v>
+        <v>520</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.2">
@@ -3230,16 +3203,16 @@
         <v>60983</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>488</v>
+        <v>479</v>
       </c>
       <c r="C64" t="s">
-        <v>519</v>
+        <v>510</v>
       </c>
       <c r="D64" s="3">
         <v>699101960</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>137</v>
+        <v>518</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.2">
@@ -3247,16 +3220,16 @@
         <v>60991</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>474</v>
+        <v>465</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>518</v>
+        <v>509</v>
       </c>
       <c r="D65" s="3">
         <v>695475025</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>137</v>
+        <v>518</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.2">
@@ -3264,13 +3237,13 @@
         <v>60992</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>478</v>
+        <v>469</v>
       </c>
       <c r="C66" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>137</v>
+        <v>518</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.2">
@@ -3278,16 +3251,16 @@
         <v>60998</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>204</v>
+        <v>521</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.2">
@@ -3295,16 +3268,16 @@
         <v>60999</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>204</v>
+        <v>521</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.2">
@@ -3312,16 +3285,16 @@
         <v>61017</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>212</v>
+        <v>522</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.2">
@@ -3329,16 +3302,16 @@
         <v>61019</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>212</v>
+        <v>522</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.2">
@@ -3346,16 +3319,16 @@
         <v>61025</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>212</v>
+        <v>522</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.2">
@@ -3363,16 +3336,16 @@
         <v>61043</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>428</v>
+        <v>419</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>212</v>
+        <v>522</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.2">
@@ -3380,16 +3353,16 @@
         <v>61046</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>212</v>
+        <v>522</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.2">
@@ -3397,16 +3370,16 @@
         <v>61065</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>212</v>
+        <v>522</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.2">
@@ -3414,16 +3387,16 @@
         <v>61073</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>212</v>
+        <v>522</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.2">
@@ -3431,16 +3404,16 @@
         <v>61074</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>212</v>
+        <v>522</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.2">
@@ -3448,16 +3421,16 @@
         <v>61079</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>212</v>
+        <v>522</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.2">
@@ -3465,16 +3438,16 @@
         <v>61080</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>426</v>
+        <v>417</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>212</v>
+        <v>522</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.2">
@@ -3482,16 +3455,16 @@
         <v>61081</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>429</v>
+        <v>420</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>212</v>
+        <v>522</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.2">
@@ -3499,13 +3472,13 @@
         <v>61092</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>0</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>212</v>
+        <v>522</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.2">
@@ -3513,16 +3486,16 @@
         <v>61100</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="C81" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>212</v>
+        <v>522</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
@@ -3530,16 +3503,16 @@
         <v>61101</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>491</v>
+        <v>482</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>492</v>
+        <v>483</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>212</v>
+        <v>522</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.2">
@@ -3547,16 +3520,16 @@
         <v>61101</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>212</v>
+        <v>522</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
@@ -3564,16 +3537,16 @@
         <v>61121</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>212</v>
+        <v>522</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.2">
@@ -3581,16 +3554,16 @@
         <v>61122</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>500</v>
+        <v>491</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>212</v>
+        <v>522</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.2">
@@ -3598,16 +3571,16 @@
         <v>61132</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>212</v>
+        <v>522</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.2">
@@ -3615,13 +3588,13 @@
         <v>61134</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>212</v>
+        <v>522</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.2">
@@ -3629,16 +3602,16 @@
         <v>61135</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>212</v>
+        <v>522</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.2">
@@ -3646,13 +3619,13 @@
         <v>62009</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>212</v>
+        <v>522</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.2">
@@ -3660,13 +3633,16 @@
         <v>62039</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>237</v>
+        <v>230</v>
+      </c>
+      <c r="E90" t="s">
+        <v>516</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.2">
@@ -3674,16 +3650,16 @@
         <v>62039</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>349</v>
+        <v>516</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.2">
@@ -3691,16 +3667,16 @@
         <v>62050</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>349</v>
+        <v>516</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.2">
@@ -3708,16 +3684,16 @@
         <v>62050</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>212</v>
+        <v>522</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.2">
@@ -3725,16 +3701,16 @@
         <v>62057</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>349</v>
+        <v>516</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.2">
@@ -3742,16 +3718,16 @@
         <v>62088</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>212</v>
+        <v>522</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.2">
@@ -3759,16 +3735,16 @@
         <v>62103</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>444</v>
+        <v>435</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>212</v>
+        <v>522</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.2">
@@ -3776,16 +3752,16 @@
         <v>62109</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>349</v>
+        <v>516</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.2">
@@ -3793,16 +3769,16 @@
         <v>62110</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>349</v>
+        <v>516</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.2">
@@ -3810,16 +3786,16 @@
         <v>62115</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>349</v>
+        <v>516</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.2">
@@ -3827,16 +3803,16 @@
         <v>62128</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>447</v>
+        <v>438</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>212</v>
+        <v>522</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.2">
@@ -3844,13 +3820,13 @@
         <v>62129</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="C101" t="s">
-        <v>519</v>
+        <v>510</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>349</v>
+        <v>516</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.2">
@@ -3858,16 +3834,16 @@
         <v>62133</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>212</v>
+        <v>522</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.2">
@@ -3875,16 +3851,16 @@
         <v>62133</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>349</v>
+        <v>516</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.2">
@@ -3892,16 +3868,16 @@
         <v>62137</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>212</v>
+        <v>522</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.2">
@@ -3909,16 +3885,16 @@
         <v>62140</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>349</v>
+        <v>516</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.2">
@@ -3926,13 +3902,13 @@
         <v>62143</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>0</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>349</v>
+        <v>516</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.2">
@@ -3940,13 +3916,13 @@
         <v>62145</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>212</v>
+        <v>522</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.2">
@@ -3954,13 +3930,13 @@
         <v>62149</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>0</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>349</v>
+        <v>516</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.2">
@@ -3968,16 +3944,16 @@
         <v>62150</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>349</v>
+        <v>516</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.2">
@@ -3985,16 +3961,16 @@
         <v>62153</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>486</v>
+        <v>477</v>
       </c>
       <c r="C110" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>349</v>
+        <v>516</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.2">
@@ -4002,16 +3978,16 @@
         <v>62154</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>501</v>
+        <v>492</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>349</v>
+        <v>516</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.2">
@@ -4019,16 +3995,16 @@
         <v>63001</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>305</v>
+        <v>523</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.2">
@@ -4036,16 +4012,16 @@
         <v>63004</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>305</v>
+        <v>523</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.2">
@@ -4053,16 +4029,16 @@
         <v>63019</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>209</v>
+        <v>524</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.2">
@@ -4070,16 +4046,16 @@
         <v>63028</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>209</v>
+        <v>524</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.2">
@@ -4087,16 +4063,16 @@
         <v>63029</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>305</v>
+        <v>523</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.2">
@@ -4104,16 +4080,16 @@
         <v>63030</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>305</v>
+        <v>523</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.2">
@@ -4121,16 +4097,16 @@
         <v>63043</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
       <c r="C118" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>138</v>
+        <v>520</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.2">
@@ -4138,16 +4114,16 @@
         <v>63048</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>305</v>
+        <v>523</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.2">
@@ -4155,16 +4131,16 @@
         <v>63049</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>305</v>
+        <v>523</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.2">
@@ -4172,10 +4148,13 @@
         <v>63053</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>503</v>
+        <v>494</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>505</v>
+        <v>496</v>
+      </c>
+      <c r="E121" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.2">
@@ -4183,16 +4162,16 @@
         <v>64017</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.2">
@@ -4200,13 +4179,13 @@
         <v>64033</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.2">
@@ -4214,16 +4193,16 @@
         <v>64041</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>212</v>
+        <v>522</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.2">
@@ -4231,16 +4210,16 @@
         <v>64043</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>139</v>
+        <v>201</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.2">
@@ -4248,16 +4227,16 @@
         <v>64054</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>139</v>
+        <v>201</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.2">
@@ -4265,13 +4244,13 @@
         <v>64055</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>410</v>
+        <v>401</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.2">
@@ -4279,16 +4258,16 @@
         <v>64063</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.2">
@@ -4296,16 +4275,16 @@
         <v>64067</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>139</v>
+        <v>201</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.2">
@@ -4313,16 +4292,16 @@
         <v>64068</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>139</v>
+        <v>201</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.2">
@@ -4330,16 +4309,16 @@
         <v>64070</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.2">
@@ -4347,13 +4326,13 @@
         <v>64072</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.2">
@@ -4361,13 +4340,13 @@
         <v>64080</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.2">
@@ -4375,16 +4354,16 @@
         <v>64091</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.2">
@@ -4392,13 +4371,13 @@
         <v>64091</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.2">
@@ -4406,16 +4385,16 @@
         <v>64905</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>139</v>
+        <v>201</v>
       </c>
     </row>
     <row r="137" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4423,13 +4402,13 @@
         <v>66004</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>204</v>
+        <v>521</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.2">
@@ -4437,16 +4416,16 @@
         <v>66467</v>
       </c>
       <c r="B138" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D138" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C138" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D138" s="3" t="s">
-        <v>95</v>
-      </c>
       <c r="E138" s="1" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.2">
@@ -4454,16 +4433,16 @@
         <v>66502</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.2">
@@ -4471,16 +4450,16 @@
         <v>66504</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.2">
@@ -4488,16 +4467,16 @@
         <v>66505</v>
       </c>
       <c r="B141" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D141" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C141" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D141" s="3" t="s">
-        <v>45</v>
-      </c>
       <c r="E141" s="1" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.2">
@@ -4505,16 +4484,16 @@
         <v>66506</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>212</v>
+        <v>522</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.2">
@@ -4522,16 +4501,16 @@
         <v>66506</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>349</v>
+        <v>516</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.2">
@@ -4539,16 +4518,16 @@
         <v>66509</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>305</v>
+        <v>523</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.2">
@@ -4556,16 +4535,16 @@
         <v>66510</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.2">
@@ -4573,16 +4552,16 @@
         <v>66513</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>469</v>
+        <v>460</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>470</v>
+        <v>461</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>471</v>
+        <v>462</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>138</v>
+        <v>520</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.2">
@@ -4590,16 +4569,16 @@
         <v>66518</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
       <c r="C147" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>137</v>
+        <v>518</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.2">
@@ -4607,13 +4586,13 @@
         <v>66520</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>137</v>
+        <v>518</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.2">
@@ -4621,16 +4600,16 @@
         <v>66524</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>212</v>
+        <v>522</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.2">
@@ -4638,16 +4617,16 @@
         <v>66525</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>137</v>
+        <v>518</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.2">
@@ -4655,16 +4634,16 @@
         <v>66531</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>305</v>
+        <v>523</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.2">
@@ -4672,16 +4651,16 @@
         <v>66538</v>
       </c>
       <c r="B152" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D152" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C152" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D152" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E152" s="1" t="s">
-        <v>521</v>
+        <v>511</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.2">
@@ -4689,16 +4668,16 @@
         <v>66544</v>
       </c>
       <c r="B153" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D153" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C153" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D153" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="E153" s="1" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.2">
@@ -4706,16 +4685,16 @@
         <v>66560</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>212</v>
+        <v>522</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.2">
@@ -4723,16 +4702,16 @@
         <v>66564</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>349</v>
+        <v>516</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.2">
@@ -4740,16 +4719,16 @@
         <v>66564</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>349</v>
+        <v>516</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.2">
@@ -4757,13 +4736,13 @@
         <v>66564</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>476</v>
+        <v>467</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>518</v>
+        <v>509</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>349</v>
+        <v>516</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.2">
@@ -4771,16 +4750,16 @@
         <v>66566</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>212</v>
+        <v>522</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.2">
@@ -4788,13 +4767,13 @@
         <v>66574</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>0</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>305</v>
+        <v>523</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.2">
@@ -4802,13 +4781,13 @@
         <v>66575</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>0</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>139</v>
+        <v>201</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.2">
@@ -4816,16 +4795,16 @@
         <v>66576</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.2">
@@ -4833,16 +4812,16 @@
         <v>66576</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.2">
@@ -4850,16 +4829,16 @@
         <v>66578</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>349</v>
+        <v>516</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.2">
@@ -4867,16 +4846,16 @@
         <v>66585</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>305</v>
+        <v>523</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.2">
@@ -4884,16 +4863,16 @@
         <v>66600</v>
       </c>
       <c r="B165" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D165" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C165" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D165" s="3" t="s">
-        <v>23</v>
-      </c>
       <c r="E165" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.2">
@@ -4901,16 +4880,16 @@
         <v>66602</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>204</v>
+        <v>521</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.2">
@@ -4918,16 +4897,16 @@
         <v>66609</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>212</v>
+        <v>522</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.2">
@@ -4935,16 +4914,16 @@
         <v>66612</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="C168" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.2">
@@ -4952,16 +4931,16 @@
         <v>66613</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="E169" s="4" t="s">
-        <v>209</v>
+        <v>524</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.2">
@@ -4969,16 +4948,16 @@
         <v>66614</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="E170" s="4" t="s">
-        <v>209</v>
+        <v>524</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.2">
@@ -4986,16 +4965,16 @@
         <v>66620</v>
       </c>
       <c r="B171" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C171" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D171" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C171" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D171" s="3" t="s">
-        <v>97</v>
-      </c>
       <c r="E171" s="1" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.2">
@@ -5003,16 +4982,16 @@
         <v>66622</v>
       </c>
       <c r="B172" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C172" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D172" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C172" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D172" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="E172" s="1" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.2">
@@ -5020,16 +4999,16 @@
         <v>66624</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="C173" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>349</v>
+        <v>516</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.2">
@@ -5037,16 +5016,16 @@
         <v>66629</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>502</v>
+        <v>493</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>349</v>
+        <v>516</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.2">
@@ -5054,13 +5033,13 @@
         <v>66631</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="C175" t="s">
-        <v>519</v>
+        <v>510</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>349</v>
+        <v>516</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.2">
@@ -5068,16 +5047,16 @@
         <v>66632</v>
       </c>
       <c r="B176" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D176" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C176" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D176" s="3" t="s">
-        <v>13</v>
-      </c>
       <c r="E176" s="2" t="s">
-        <v>1</v>
+        <v>517</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.2">
@@ -5085,16 +5064,16 @@
         <v>66641</v>
       </c>
       <c r="B177" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C177" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D177" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C177" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D177" s="3" t="s">
-        <v>7</v>
-      </c>
       <c r="E177" s="2" t="s">
-        <v>1</v>
+        <v>517</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.2">
@@ -5102,16 +5081,16 @@
         <v>66642</v>
       </c>
       <c r="B178" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C178" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D178" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C178" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D178" s="3" t="s">
-        <v>89</v>
-      </c>
       <c r="E178" s="1" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.2">
@@ -5119,13 +5098,13 @@
         <v>66646</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>438</v>
+        <v>429</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>212</v>
+        <v>522</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.2">
@@ -5133,16 +5112,16 @@
         <v>66660</v>
       </c>
       <c r="B180" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C180" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D180" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C180" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D180" s="3" t="s">
-        <v>83</v>
-      </c>
       <c r="E180" s="1" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.2">
@@ -5150,16 +5129,16 @@
         <v>66662</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>441</v>
+        <v>432</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>212</v>
+        <v>522</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.2">
@@ -5167,16 +5146,16 @@
         <v>66664</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="C182" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>349</v>
+        <v>516</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.2">
@@ -5184,16 +5163,16 @@
         <v>66667</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>437</v>
+        <v>428</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>212</v>
+        <v>522</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.2">
@@ -5201,13 +5180,13 @@
         <v>66668</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>465</v>
+        <v>456</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.2">
@@ -5215,16 +5194,16 @@
         <v>66673</v>
       </c>
       <c r="B185" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C185" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D185" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C185" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D185" s="3" t="s">
-        <v>85</v>
-      </c>
       <c r="E185" s="1" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.2">
@@ -5232,13 +5211,13 @@
         <v>66685</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>137</v>
+        <v>518</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.2">
@@ -5246,16 +5225,16 @@
         <v>66694</v>
       </c>
       <c r="B187" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C187" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D187" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C187" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D187" s="3" t="s">
-        <v>29</v>
-      </c>
       <c r="E187" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.2">
@@ -5263,16 +5242,16 @@
         <v>66697</v>
       </c>
       <c r="B188" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C188" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D188" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="C188" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D188" s="3" t="s">
-        <v>111</v>
-      </c>
       <c r="E188" s="1" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.2">
@@ -5280,16 +5259,16 @@
         <v>66700</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>349</v>
+        <v>516</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.2">
@@ -5297,16 +5276,16 @@
         <v>66704</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>436</v>
+        <v>427</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>212</v>
+        <v>522</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.2">
@@ -5314,16 +5293,16 @@
         <v>66705</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="C191" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>212</v>
+        <v>522</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.2">
@@ -5331,16 +5310,16 @@
         <v>66708</v>
       </c>
       <c r="B192" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C192" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D192" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C192" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D192" s="3" t="s">
-        <v>15</v>
-      </c>
       <c r="E192" s="2" t="s">
-        <v>1</v>
+        <v>517</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.2">
@@ -5348,16 +5327,16 @@
         <v>66715</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="C193" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>139</v>
+        <v>201</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.2">
@@ -5365,16 +5344,16 @@
         <v>66720</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>475</v>
+        <v>466</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>518</v>
+        <v>509</v>
       </c>
       <c r="D194" s="3">
         <v>678874714</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>137</v>
+        <v>518</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.2">
@@ -5382,16 +5361,16 @@
         <v>66722</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D195" s="3" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>212</v>
+        <v>522</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.2">
@@ -5399,16 +5378,16 @@
         <v>66726</v>
       </c>
       <c r="B196" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C196" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D196" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C196" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D196" s="3" t="s">
-        <v>73</v>
-      </c>
       <c r="E196" s="1" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.2">
@@ -5416,13 +5395,13 @@
         <v>66730</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>212</v>
+        <v>522</v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.2">
@@ -5430,16 +5409,16 @@
         <v>66731</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="C198" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>139</v>
+        <v>201</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.2">
@@ -5447,16 +5426,16 @@
         <v>66733</v>
       </c>
       <c r="B199" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C199" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D199" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C199" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D199" s="3" t="s">
-        <v>93</v>
-      </c>
       <c r="E199" s="1" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.2">
@@ -5464,16 +5443,16 @@
         <v>66735</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="C200" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.2">
@@ -5481,16 +5460,16 @@
         <v>66738</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>464</v>
+        <v>455</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="E201" s="4" t="s">
-        <v>209</v>
+        <v>524</v>
       </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.2">
@@ -5498,13 +5477,16 @@
         <v>66739</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>466</v>
+        <v>457</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>238</v>
+        <v>231</v>
+      </c>
+      <c r="E202" t="s">
+        <v>516</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.2">
@@ -5512,16 +5494,16 @@
         <v>66741</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="C203" s="3" t="s">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.2">
@@ -5529,16 +5511,16 @@
         <v>66742</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>463</v>
+        <v>454</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="E204" s="4" t="s">
-        <v>209</v>
+        <v>524</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.2">
@@ -5546,16 +5528,16 @@
         <v>66744</v>
       </c>
       <c r="B205" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C205" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D205" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="C205" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D205" s="3" t="s">
-        <v>125</v>
-      </c>
       <c r="E205" s="1" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.2">
@@ -5563,16 +5545,16 @@
         <v>66745</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>517</v>
+        <v>508</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="E206" s="2" t="s">
-        <v>212</v>
+        <v>522</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.2">
@@ -5580,16 +5562,16 @@
         <v>66748</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="C207" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>212</v>
+        <v>522</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.2">
@@ -5597,16 +5579,16 @@
         <v>66749</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="C208" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="E208" s="2" t="s">
-        <v>139</v>
+        <v>201</v>
       </c>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.2">
@@ -5614,16 +5596,16 @@
         <v>66750</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>495</v>
+        <v>486</v>
       </c>
       <c r="C209" s="3" t="s">
-        <v>492</v>
+        <v>483</v>
       </c>
       <c r="D209" s="3" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="E209" s="2" t="s">
-        <v>212</v>
+        <v>522</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.2">
@@ -5631,13 +5613,13 @@
         <v>66751</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>204</v>
+        <v>521</v>
       </c>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.2">
@@ -5645,16 +5627,16 @@
         <v>66753</v>
       </c>
       <c r="B211" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C211" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D211" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C211" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D211" s="3" t="s">
-        <v>107</v>
-      </c>
       <c r="E211" s="1" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.2">
@@ -5662,16 +5644,16 @@
         <v>66755</v>
       </c>
       <c r="B212" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C212" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D212" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="C212" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D212" s="3" t="s">
-        <v>115</v>
-      </c>
       <c r="E212" s="1" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.2">
@@ -5679,16 +5661,16 @@
         <v>66756</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="C213" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D213" s="3" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="E213" s="2" t="s">
-        <v>139</v>
+        <v>201</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.2">
@@ -5696,16 +5678,16 @@
         <v>66757</v>
       </c>
       <c r="B214" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C214" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D214" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C214" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D214" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E214" s="1" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.2">
@@ -5713,16 +5695,16 @@
         <v>66758</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>494</v>
+        <v>485</v>
       </c>
       <c r="C215" s="3" t="s">
-        <v>492</v>
+        <v>483</v>
       </c>
       <c r="D215" s="3" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="E215" t="s">
-        <v>523</v>
+        <v>512</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.2">
@@ -5730,16 +5712,16 @@
         <v>66759</v>
       </c>
       <c r="B216" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C216" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D216" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C216" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D216" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="E216" s="1" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.2">
@@ -5747,16 +5729,16 @@
         <v>66768</v>
       </c>
       <c r="B217" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C217" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D217" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C217" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D217" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="E217" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.2">
@@ -5764,16 +5746,16 @@
         <v>66770</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>490</v>
+        <v>481</v>
       </c>
       <c r="C218" t="s">
-        <v>519</v>
+        <v>510</v>
       </c>
       <c r="D218" s="3" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="E218" s="2" t="s">
-        <v>212</v>
+        <v>522</v>
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.2">
@@ -5781,16 +5763,16 @@
         <v>66772</v>
       </c>
       <c r="B219" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C219" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D219" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C219" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D219" s="3" t="s">
-        <v>18</v>
-      </c>
       <c r="E219" s="2" t="s">
-        <v>1</v>
+        <v>517</v>
       </c>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.2">
@@ -5798,16 +5780,16 @@
         <v>66773</v>
       </c>
       <c r="B220" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C220" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D220" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C220" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D220" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="E220" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.2">
@@ -5815,13 +5797,13 @@
         <v>66774</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C221" s="2" t="s">
         <v>0</v>
       </c>
       <c r="E221" s="2" t="s">
-        <v>1</v>
+        <v>517</v>
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.2">
@@ -5829,16 +5811,16 @@
         <v>66775</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="C222" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D222" s="3" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="E222" s="2" t="s">
-        <v>139</v>
+        <v>201</v>
       </c>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.2">
@@ -5846,16 +5828,16 @@
         <v>66776</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="C223" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D223" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E223" s="2" t="s">
-        <v>212</v>
+        <v>522</v>
       </c>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.2">
@@ -5863,16 +5845,16 @@
         <v>66777</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C224" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D224" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E224" s="2" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.2">
@@ -5880,16 +5862,16 @@
         <v>66777</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C225" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D225" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.2">
@@ -5897,16 +5879,16 @@
         <v>66778</v>
       </c>
       <c r="B226" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C226" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D226" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C226" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D226" s="3" t="s">
-        <v>117</v>
-      </c>
       <c r="E226" s="1" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.2">
@@ -5914,16 +5896,16 @@
         <v>66779</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
       <c r="C227" s="3" t="s">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="D227" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E227" s="2" t="s">
-        <v>138</v>
+        <v>520</v>
       </c>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.2">
@@ -5931,16 +5913,16 @@
         <v>66780</v>
       </c>
       <c r="B228" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C228" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D228" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="C228" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D228" s="3" t="s">
-        <v>121</v>
-      </c>
       <c r="E228" s="1" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.2">
@@ -5948,13 +5930,13 @@
         <v>66785</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C229" s="2" t="s">
         <v>0</v>
       </c>
       <c r="E229" s="2" t="s">
-        <v>1</v>
+        <v>517</v>
       </c>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.2">
@@ -5962,16 +5944,16 @@
         <v>66786</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
       <c r="C230" t="s">
+        <v>233</v>
+      </c>
+      <c r="D230" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="D230" s="3" t="s">
-        <v>247</v>
-      </c>
       <c r="E230" s="2" t="s">
-        <v>137</v>
+        <v>518</v>
       </c>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.2">
@@ -5979,16 +5961,16 @@
         <v>66793</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="C231" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D231" s="3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="E231" s="2" t="s">
-        <v>305</v>
+        <v>523</v>
       </c>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.2">
@@ -5996,16 +5978,16 @@
         <v>66794</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="C232" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D232" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="E232" s="2" t="s">
-        <v>212</v>
+        <v>522</v>
       </c>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.2">
@@ -6013,16 +5995,16 @@
         <v>66798</v>
       </c>
       <c r="B233" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C233" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D233" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="C233" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D233" s="3" t="s">
-        <v>128</v>
-      </c>
       <c r="E233" s="1" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.2">
@@ -6030,16 +6012,16 @@
         <v>66799</v>
       </c>
       <c r="B234" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C234" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D234" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C234" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D234" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="E234" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.2">
@@ -6047,16 +6029,16 @@
         <v>66800</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="C235" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D235" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="E235" s="2" t="s">
-        <v>305</v>
+        <v>523</v>
       </c>
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.2">
@@ -6064,16 +6046,16 @@
         <v>66801</v>
       </c>
       <c r="B236" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C236" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D236" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="C236" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D236" s="2" t="s">
-        <v>130</v>
-      </c>
       <c r="E236" s="1" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.2">
@@ -6081,16 +6063,16 @@
         <v>66802</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="C237" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D237" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="E237" s="2" t="s">
-        <v>212</v>
+        <v>522</v>
       </c>
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.2">
@@ -6098,13 +6080,16 @@
         <v>66803</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="C238" s="3" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
       <c r="D238" s="3" t="s">
-        <v>268</v>
+        <v>261</v>
+      </c>
+      <c r="E238" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.2">
@@ -6112,13 +6097,13 @@
         <v>66805</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C239" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E239" s="2" t="s">
-        <v>138</v>
+        <v>520</v>
       </c>
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.2">
@@ -6126,13 +6111,13 @@
         <v>66806</v>
       </c>
       <c r="B240" s="3" t="s">
-        <v>454</v>
+        <v>445</v>
       </c>
       <c r="C240" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="E240" s="2" t="s">
         <v>517</v>
-      </c>
-      <c r="E240" s="2" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.2">
@@ -6140,16 +6125,16 @@
         <v>66808</v>
       </c>
       <c r="B241" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C241" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D241" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C241" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D241" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="E241" s="1" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.2">
@@ -6157,16 +6142,16 @@
         <v>66809</v>
       </c>
       <c r="B242" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C242" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D242" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C242" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D242" s="3" t="s">
-        <v>134</v>
-      </c>
       <c r="E242" s="1" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.2">
@@ -6174,501 +6159,566 @@
         <v>66810</v>
       </c>
       <c r="B243" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C243" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D243" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="C243" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D243" s="3" t="s">
-        <v>136</v>
-      </c>
       <c r="E243" s="1" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B244" s="3" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="C244" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D244" s="3" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="E244" s="2" t="s">
-        <v>212</v>
+        <v>522</v>
       </c>
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B245" s="3" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="C245" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E245" s="4" t="s">
-        <v>209</v>
+        <v>524</v>
       </c>
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B246" s="3" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="C246" s="2" t="s">
         <v>0</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B247" s="3" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
       <c r="C247" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D247" s="3" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="E247" s="2" t="s">
-        <v>212</v>
+        <v>522</v>
       </c>
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B248" s="3" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="C248" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D248" s="3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E248" s="2" t="s">
-        <v>139</v>
+        <v>201</v>
       </c>
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A249" s="3"/>
       <c r="B249" s="3" t="s">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="C249" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D249" s="3" t="s">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="E249" s="2" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B250" s="3" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="C250" s="2" t="s">
         <v>0</v>
       </c>
       <c r="E250" s="2" t="s">
-        <v>139</v>
+        <v>201</v>
       </c>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B251" s="3" t="s">
-        <v>508</v>
+        <v>499</v>
       </c>
       <c r="C251" s="3" t="s">
-        <v>509</v>
+        <v>500</v>
       </c>
       <c r="D251" s="3" t="s">
-        <v>269</v>
+        <v>262</v>
+      </c>
+      <c r="E251" t="s">
+        <v>520</v>
       </c>
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B252" s="3" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="C252" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="E252" s="2" t="s">
         <v>517</v>
-      </c>
-      <c r="E252" s="2" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A253" s="3"/>
       <c r="B253" s="3" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="C253" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D253" s="3" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="E253" s="2" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B254" s="3" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="C254" s="3" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="E254" s="2" t="s">
-        <v>138</v>
+        <v>520</v>
       </c>
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B255" s="3" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="C255" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E255" s="2" t="s">
-        <v>204</v>
+        <v>521</v>
       </c>
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B256" s="3" t="s">
-        <v>459</v>
+        <v>450</v>
       </c>
       <c r="C256" s="3" t="s">
-        <v>458</v>
+        <v>449</v>
       </c>
       <c r="D256" s="3">
         <v>677255778</v>
       </c>
       <c r="E256" s="2" t="s">
-        <v>138</v>
+        <v>520</v>
       </c>
     </row>
     <row r="257" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B257" s="3" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="C257" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D257" s="3" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="E257" s="2" t="s">
-        <v>212</v>
+        <v>522</v>
       </c>
     </row>
     <row r="258" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B258" s="3" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="C258" s="2" t="s">
         <v>0</v>
       </c>
       <c r="E258" s="2" t="s">
-        <v>349</v>
+        <v>516</v>
       </c>
     </row>
     <row r="259" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B259" s="3" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="C259" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D259" s="3" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="E259" s="2" t="s">
-        <v>212</v>
+        <v>522</v>
       </c>
     </row>
     <row r="260" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B260" s="3" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="C260" s="2" t="s">
         <v>0</v>
       </c>
       <c r="E260" s="2" t="s">
-        <v>349</v>
+        <v>516</v>
       </c>
     </row>
     <row r="261" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B261" s="3" t="s">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="C261" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D261" s="3" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="E261" s="2" t="s">
-        <v>212</v>
+        <v>522</v>
       </c>
     </row>
     <row r="262" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B262" s="3" t="s">
-        <v>515</v>
+        <v>506</v>
       </c>
       <c r="C262" s="3" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="D262" s="3" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="E262" s="2" t="s">
-        <v>349</v>
+        <v>516</v>
       </c>
     </row>
     <row r="263" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B263" s="3" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
       <c r="C263" s="3" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="E263" s="2" t="s">
-        <v>138</v>
+        <v>520</v>
       </c>
     </row>
     <row r="264" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B264" s="3" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="C264" s="3" t="s">
-        <v>458</v>
+        <v>449</v>
       </c>
       <c r="E264" s="2" t="s">
-        <v>138</v>
+        <v>520</v>
       </c>
     </row>
     <row r="265" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B265" s="3" t="s">
-        <v>473</v>
+        <v>464</v>
       </c>
       <c r="C265" s="3" t="s">
-        <v>470</v>
+        <v>461</v>
       </c>
       <c r="D265" s="3" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="E265" s="2" t="s">
-        <v>212</v>
+        <v>522</v>
       </c>
     </row>
     <row r="266" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B266" s="3" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="C266" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E266" s="2" t="s">
-        <v>138</v>
+        <v>520</v>
       </c>
     </row>
     <row r="267" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B267" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C267" s="2" t="s">
         <v>0</v>
       </c>
       <c r="E267" s="2" t="s">
-        <v>1</v>
+        <v>517</v>
       </c>
     </row>
     <row r="268" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B268" s="3" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="C268" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E268" s="2" t="s">
-        <v>138</v>
+        <v>520</v>
       </c>
     </row>
     <row r="269" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B269" s="3" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
       <c r="C269" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="D269" s="3" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="E269" s="2" t="s">
-        <v>137</v>
+        <v>518</v>
       </c>
     </row>
     <row r="270" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B270" s="3" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="C270" s="3" t="s">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="D270" s="3" t="s">
-        <v>239</v>
+        <v>232</v>
+      </c>
+      <c r="E270" t="s">
+        <v>520</v>
       </c>
     </row>
     <row r="271" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B271" s="3" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="C271" s="2" t="s">
         <v>0</v>
       </c>
       <c r="E271" s="2" t="s">
-        <v>305</v>
+        <v>523</v>
       </c>
     </row>
     <row r="272" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B272" s="3" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="C272" s="2" t="s">
         <v>0</v>
       </c>
       <c r="E272" s="2" t="s">
-        <v>305</v>
+        <v>523</v>
       </c>
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B273" s="3" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="C273" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D273" s="3" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="E273" s="2" t="s">
-        <v>204</v>
+        <v>521</v>
       </c>
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B274" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="C274" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="C274" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E274" s="2" t="s">
-        <v>349</v>
+        <v>516</v>
       </c>
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B275" s="3" t="s">
-        <v>472</v>
+        <v>463</v>
       </c>
       <c r="C275" s="3" t="s">
-        <v>470</v>
+        <v>461</v>
       </c>
       <c r="D275" s="3" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B276" s="3" t="s">
-        <v>514</v>
+        <v>505</v>
       </c>
       <c r="C276" s="3" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="E276" s="2" t="s">
-        <v>212</v>
+        <v>522</v>
       </c>
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B277" s="3" t="s">
-        <v>510</v>
+        <v>501</v>
       </c>
       <c r="C277" s="3" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
       <c r="D277" s="3" t="s">
-        <v>511</v>
+        <v>502</v>
+      </c>
+      <c r="E277" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B278" s="3" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="C278" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E278" s="2" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B279" s="3" t="s">
-        <v>516</v>
+        <v>507</v>
       </c>
       <c r="C279" s="3" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B280" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="C280" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="C280" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E280" s="2" t="s">
-        <v>349</v>
+        <v>516</v>
       </c>
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B281" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="C281" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E281" s="4" t="s">
-        <v>209</v>
+        <v>524</v>
       </c>
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B282" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="C282" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="C282" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E282" s="2" t="s">
-        <v>349</v>
+        <v>516</v>
       </c>
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
-        <v>525</v>
+        <v>514</v>
       </c>
       <c r="B283" s="3"/>
       <c r="C283" s="3"/>
       <c r="E283">
         <f>SUBTOTAL(103,presta_soins[TYPE])</f>
-        <v>274</v>
-      </c>
+        <v>281</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B284" s="3"/>
+      <c r="C284" s="3"/>
+    </row>
+    <row r="285" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B285" s="3"/>
+      <c r="C285" s="3"/>
+    </row>
+    <row r="286" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B286" s="3"/>
+      <c r="C286" s="3"/>
+    </row>
+    <row r="287" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B287" s="3"/>
+      <c r="C287" s="3"/>
+    </row>
+    <row r="288" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B288" s="3"/>
+      <c r="C288" s="3"/>
+    </row>
+    <row r="289" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B289" s="3"/>
+      <c r="C289" s="3"/>
+    </row>
+    <row r="290" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B290" s="3"/>
+      <c r="C290" s="3"/>
+    </row>
+    <row r="291" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B291" s="3"/>
+      <c r="C291" s="3"/>
+    </row>
+    <row r="292" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B292" s="3"/>
+      <c r="C292" s="3"/>
+    </row>
+    <row r="293" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B293" s="3"/>
+      <c r="C293" s="3"/>
+    </row>
+    <row r="294" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B294" s="3"/>
+      <c r="C294" s="3"/>
+    </row>
+    <row r="295" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B295" s="3"/>
+      <c r="C295" s="3"/>
+    </row>
+    <row r="296" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B296" s="3"/>
+      <c r="C296" s="3"/>
+    </row>
+    <row r="297" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B297" s="3"/>
+      <c r="C297" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
